--- a/reportstellarsoiree.xlsx
+++ b/reportstellarsoiree.xlsx
@@ -1,21 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TABITA\Hwa Ind Prom\2025\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEB50FD-C4A2-487D-956E-238E69A710CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1797">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="1829">
   <si>
     <t>No</t>
   </si>
@@ -5406,21 +5424,116 @@
   </si>
   <si>
     <t>https://udr.reddonedigital.com/VincentEzarNovericoSuryadi/StellarSoiree/82395/375</t>
+  </si>
+  <si>
+    <t>12E-01</t>
+  </si>
+  <si>
+    <t>12E-02</t>
+  </si>
+  <si>
+    <t>12E-03</t>
+  </si>
+  <si>
+    <t>12E-04</t>
+  </si>
+  <si>
+    <t>12E-05</t>
+  </si>
+  <si>
+    <t>12E-06</t>
+  </si>
+  <si>
+    <t>12E-07</t>
+  </si>
+  <si>
+    <t>12E-08</t>
+  </si>
+  <si>
+    <t>12E-09</t>
+  </si>
+  <si>
+    <t>12E-10</t>
+  </si>
+  <si>
+    <t>12E-11</t>
+  </si>
+  <si>
+    <t>12E-12</t>
+  </si>
+  <si>
+    <t>12E-13</t>
+  </si>
+  <si>
+    <t>12E-14</t>
+  </si>
+  <si>
+    <t>12E-15</t>
+  </si>
+  <si>
+    <t>12E-16</t>
+  </si>
+  <si>
+    <t>12E-17</t>
+  </si>
+  <si>
+    <t>12E-18</t>
+  </si>
+  <si>
+    <t>12E-19</t>
+  </si>
+  <si>
+    <t>12E-20</t>
+  </si>
+  <si>
+    <t>12E-21</t>
+  </si>
+  <si>
+    <t>12E-22</t>
+  </si>
+  <si>
+    <t>12E-23</t>
+  </si>
+  <si>
+    <t>12E-24</t>
+  </si>
+  <si>
+    <t>12E-25</t>
+  </si>
+  <si>
+    <t>12E-26</t>
+  </si>
+  <si>
+    <t>12E-27</t>
+  </si>
+  <si>
+    <t>12E-28</t>
+  </si>
+  <si>
+    <t>12E-29</t>
+  </si>
+  <si>
+    <t>12E-30</t>
+  </si>
+  <si>
+    <t>12E-31</t>
+  </si>
+  <si>
+    <t>12E-32</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -5444,14 +5557,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -5741,14 +5863,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M464"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5789,7 +5908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5815,7 +5934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5841,7 +5960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5864,7 +5983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5887,7 +6006,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5910,7 +6029,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5936,7 +6055,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5959,7 +6078,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5982,7 +6101,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -6005,7 +6124,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -6028,7 +6147,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -6051,7 +6170,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -6074,7 +6193,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -6097,7 +6216,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6123,7 +6242,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6146,7 +6265,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6169,7 +6288,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -6192,7 +6311,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -6215,7 +6334,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -6238,7 +6357,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -6261,7 +6380,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -6287,7 +6406,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -6310,7 +6429,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -6336,7 +6455,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -6359,7 +6478,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -6382,7 +6501,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -6408,7 +6527,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -6431,7 +6550,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -6454,7 +6573,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -6480,7 +6599,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -6506,7 +6625,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -6532,7 +6651,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -6555,7 +6674,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -6581,7 +6700,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6604,7 +6723,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6627,7 +6746,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6650,7 +6769,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6673,7 +6792,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6696,7 +6815,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6719,7 +6838,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6742,7 +6861,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6768,7 +6887,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6794,7 +6913,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -6817,7 +6936,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6843,7 +6962,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6866,7 +6985,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:13">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6889,7 +7008,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6912,7 +7031,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6935,7 +7054,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6961,7 +7080,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6984,7 +7103,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -7007,7 +7126,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -7030,7 +7149,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -7053,7 +7172,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -7076,7 +7195,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -7099,7 +7218,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -7122,7 +7241,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -7145,7 +7264,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -7171,7 +7290,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -7194,7 +7313,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -7217,7 +7336,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -7240,7 +7359,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -7263,7 +7382,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -7286,7 +7405,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -7312,7 +7431,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -7335,7 +7454,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -7358,7 +7477,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -7381,7 +7500,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -7404,7 +7523,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -7430,7 +7549,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -7453,7 +7572,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -7476,7 +7595,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -7499,7 +7618,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -7522,7 +7641,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -7545,7 +7664,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -7568,7 +7687,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -7591,7 +7710,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -7617,7 +7736,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -7640,7 +7759,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -7663,7 +7782,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -7686,7 +7805,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -7709,7 +7828,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7732,7 +7851,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7758,7 +7877,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7781,7 +7900,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7804,7 +7923,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7827,7 +7946,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7850,7 +7969,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7873,7 +7992,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7896,7 +8015,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7919,7 +8038,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7945,7 +8064,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7971,7 +8090,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7997,7 +8116,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -8023,7 +8142,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -8049,7 +8168,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -8075,7 +8194,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -8101,7 +8220,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -8127,7 +8246,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -8153,7 +8272,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -8179,7 +8298,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -8205,7 +8324,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -8231,7 +8350,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -8257,7 +8376,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -8283,7 +8402,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -8309,7 +8428,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -8335,7 +8454,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -8361,7 +8480,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -8387,7 +8506,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -8413,7 +8532,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -8439,7 +8558,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -8465,7 +8584,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -8491,7 +8610,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -8517,7 +8636,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -8543,7 +8662,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -8569,7 +8688,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -8595,7 +8714,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -8621,7 +8740,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -8647,7 +8766,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -8673,7 +8792,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8699,7 +8818,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8725,7 +8844,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8751,7 +8870,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="124" spans="1:13">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8777,7 +8896,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8803,7 +8922,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="126" spans="1:13">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8832,7 +8951,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="127" spans="1:13">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8858,7 +8977,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="128" spans="1:13">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8884,7 +9003,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="129" spans="1:13">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8910,7 +9029,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="130" spans="1:13">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8936,7 +9055,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="131" spans="1:13">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8962,7 +9081,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="132" spans="1:13">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8988,7 +9107,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="133" spans="1:13">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -9014,7 +9133,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="134" spans="1:13">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -9040,7 +9159,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -9066,7 +9185,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -9092,7 +9211,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -9118,7 +9237,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="138" spans="1:13">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -9144,7 +9263,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="139" spans="1:13">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -9170,7 +9289,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="140" spans="1:13">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -9196,7 +9315,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="141" spans="1:13">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -9222,7 +9341,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="142" spans="1:13">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -9248,7 +9367,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -9277,7 +9396,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -9303,7 +9422,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="145" spans="1:13">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -9329,7 +9448,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -9355,7 +9474,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -9381,7 +9500,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="148" spans="1:13">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -9407,7 +9526,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="149" spans="1:13">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -9433,7 +9552,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -9459,7 +9578,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="151" spans="1:13">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -9485,7 +9604,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -9511,7 +9630,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="153" spans="1:13">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -9537,7 +9656,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="154" spans="1:13">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -9563,7 +9682,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="155" spans="1:13">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -9589,7 +9708,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -9618,7 +9737,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="157" spans="1:13">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -9644,7 +9763,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -9670,7 +9789,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="159" spans="1:13">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9696,7 +9815,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="160" spans="1:13">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9722,7 +9841,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="161" spans="1:13">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9748,7 +9867,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="162" spans="1:13">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9774,7 +9893,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="163" spans="1:13">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9800,7 +9919,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="164" spans="1:13">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9826,7 +9945,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="165" spans="1:13">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9852,7 +9971,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="166" spans="1:13">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9878,7 +9997,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="167" spans="1:13">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9907,7 +10026,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="168" spans="1:13">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9933,7 +10052,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="169" spans="1:13">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9959,7 +10078,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="170" spans="1:13">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9985,7 +10104,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="171" spans="1:13">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -10011,7 +10130,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="172" spans="1:13">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -10037,7 +10156,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="173" spans="1:13">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -10063,7 +10182,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="174" spans="1:13">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -10089,7 +10208,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="175" spans="1:13">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -10115,7 +10234,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="176" spans="1:13">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -10141,7 +10260,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="177" spans="1:13">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -10167,7 +10286,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="178" spans="1:13">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -10193,7 +10312,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="179" spans="1:13">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -10219,7 +10338,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="180" spans="1:13">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -10245,7 +10364,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="181" spans="1:13">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -10271,7 +10390,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="182" spans="1:13">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -10297,7 +10416,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="183" spans="1:13">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -10323,7 +10442,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="184" spans="1:13">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -10349,7 +10468,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="185" spans="1:13">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -10375,7 +10494,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="186" spans="1:13">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -10401,7 +10520,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="187" spans="1:13">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -10427,7 +10546,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="188" spans="1:13">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -10453,7 +10572,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="189" spans="1:13">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -10479,7 +10598,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="190" spans="1:13">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -10505,7 +10624,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="191" spans="1:13">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -10531,7 +10650,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="192" spans="1:13">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -10560,7 +10679,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="193" spans="1:13">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -10586,7 +10705,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="194" spans="1:13">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -10612,7 +10731,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="195" spans="1:13">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -10638,7 +10757,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="196" spans="1:13">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -10664,7 +10783,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="197" spans="1:13">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10690,7 +10809,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="198" spans="1:13">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10716,7 +10835,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="199" spans="1:13">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10742,7 +10861,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="200" spans="1:13">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10768,7 +10887,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="201" spans="1:13">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10794,7 +10913,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10820,7 +10939,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10846,7 +10965,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="204" spans="1:13">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10872,7 +10991,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="205" spans="1:13">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10901,7 +11020,7 @@
         <v>767</v>
       </c>
     </row>
-    <row r="206" spans="1:13">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10927,7 +11046,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="207" spans="1:13">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10953,7 +11072,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="208" spans="1:13">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10979,7 +11098,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="209" spans="1:13">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -11008,7 +11127,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="210" spans="1:13">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -11034,7 +11153,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="211" spans="1:13">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -11060,7 +11179,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="212" spans="1:13">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -11086,7 +11205,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -11112,7 +11231,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="214" spans="1:13">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -11138,7 +11257,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="215" spans="1:13">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -11164,7 +11283,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -11190,7 +11309,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="217" spans="1:13">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -11216,7 +11335,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="218" spans="1:13">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -11242,7 +11361,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="219" spans="1:13">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -11271,7 +11390,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="220" spans="1:13">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -11284,8 +11403,8 @@
       <c r="F220">
         <v>6282142492145</v>
       </c>
-      <c r="G220">
-        <v>1.2</v>
+      <c r="G220" s="1" t="s">
+        <v>1797</v>
       </c>
       <c r="J220" t="s">
         <v>15</v>
@@ -11297,7 +11416,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="221" spans="1:13">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -11310,8 +11429,8 @@
       <c r="F221">
         <v>6281236119406</v>
       </c>
-      <c r="G221">
-        <v>0.12</v>
+      <c r="G221" s="1" t="s">
+        <v>1798</v>
       </c>
       <c r="J221" t="s">
         <v>15</v>
@@ -11326,7 +11445,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="222" spans="1:13">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -11339,8 +11458,8 @@
       <c r="F222">
         <v>6281559801387</v>
       </c>
-      <c r="G222">
-        <v>0.012</v>
+      <c r="G222" s="1" t="s">
+        <v>1799</v>
       </c>
       <c r="J222" t="s">
         <v>15</v>
@@ -11352,7 +11471,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="223" spans="1:13">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -11365,8 +11484,8 @@
       <c r="F223">
         <v>6287859595928</v>
       </c>
-      <c r="G223">
-        <v>0.0012</v>
+      <c r="G223" s="1" t="s">
+        <v>1800</v>
       </c>
       <c r="J223" t="s">
         <v>43</v>
@@ -11378,7 +11497,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="224" spans="1:13">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -11391,8 +11510,8 @@
       <c r="F224">
         <v>6287779273966</v>
       </c>
-      <c r="G224">
-        <v>0.00012</v>
+      <c r="G224" s="1" t="s">
+        <v>1801</v>
       </c>
       <c r="J224" t="s">
         <v>15</v>
@@ -11404,7 +11523,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="225" spans="1:13">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -11417,8 +11536,8 @@
       <c r="F225">
         <v>628113042112</v>
       </c>
-      <c r="G225">
-        <v>1.2E-5</v>
+      <c r="G225" s="1" t="s">
+        <v>1802</v>
       </c>
       <c r="J225" t="s">
         <v>15</v>
@@ -11430,7 +11549,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="226" spans="1:13">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -11443,8 +11562,8 @@
       <c r="F226">
         <v>6282191225567</v>
       </c>
-      <c r="G226">
-        <v>1.2E-6</v>
+      <c r="G226" s="1" t="s">
+        <v>1803</v>
       </c>
       <c r="J226" t="s">
         <v>15</v>
@@ -11456,7 +11575,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -11469,8 +11588,8 @@
       <c r="F227">
         <v>62881026473277</v>
       </c>
-      <c r="G227">
-        <v>1.2E-7</v>
+      <c r="G227" s="1" t="s">
+        <v>1804</v>
       </c>
       <c r="J227" t="s">
         <v>15</v>
@@ -11482,7 +11601,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="228" spans="1:13">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -11495,8 +11614,8 @@
       <c r="F228">
         <v>6281359230611</v>
       </c>
-      <c r="G228">
-        <v>1.2E-8</v>
+      <c r="G228" s="1" t="s">
+        <v>1805</v>
       </c>
       <c r="J228" t="s">
         <v>15</v>
@@ -11508,7 +11627,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="229" spans="1:13">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -11521,8 +11640,8 @@
       <c r="F229">
         <v>6281216058301</v>
       </c>
-      <c r="G229">
-        <v>1.2E-9</v>
+      <c r="G229" s="1" t="s">
+        <v>1806</v>
       </c>
       <c r="J229" t="s">
         <v>15</v>
@@ -11534,7 +11653,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="230" spans="1:13">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -11547,8 +11666,8 @@
       <c r="F230">
         <v>6281251094584</v>
       </c>
-      <c r="G230">
-        <v>1.2E-10</v>
+      <c r="G230" s="1" t="s">
+        <v>1807</v>
       </c>
       <c r="J230" t="s">
         <v>15</v>
@@ -11560,7 +11679,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="231" spans="1:13">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -11573,8 +11692,8 @@
       <c r="F231">
         <v>6289686105579</v>
       </c>
-      <c r="G231">
-        <v>1.2E-11</v>
+      <c r="G231" s="1" t="s">
+        <v>1808</v>
       </c>
       <c r="J231" t="s">
         <v>15</v>
@@ -11586,7 +11705,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="232" spans="1:13">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -11599,8 +11718,8 @@
       <c r="F232">
         <v>6285384984543</v>
       </c>
-      <c r="G232">
-        <v>1.2E-12</v>
+      <c r="G232" s="1" t="s">
+        <v>1809</v>
       </c>
       <c r="J232" t="s">
         <v>15</v>
@@ -11615,7 +11734,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="233" spans="1:13">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -11628,8 +11747,8 @@
       <c r="F233">
         <v>6285257140633</v>
       </c>
-      <c r="G233">
-        <v>1.2E-13</v>
+      <c r="G233" s="1" t="s">
+        <v>1810</v>
       </c>
       <c r="J233" t="s">
         <v>15</v>
@@ -11641,7 +11760,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="234" spans="1:13">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -11654,8 +11773,8 @@
       <c r="F234">
         <v>628113578875</v>
       </c>
-      <c r="G234">
-        <v>1.2E-14</v>
+      <c r="G234" s="1" t="s">
+        <v>1811</v>
       </c>
       <c r="J234" t="s">
         <v>15</v>
@@ -11667,7 +11786,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="235" spans="1:13">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -11680,8 +11799,8 @@
       <c r="F235">
         <v>6282123459682</v>
       </c>
-      <c r="G235">
-        <v>1.2E-15</v>
+      <c r="G235" s="1" t="s">
+        <v>1812</v>
       </c>
       <c r="J235" t="s">
         <v>15</v>
@@ -11693,7 +11812,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="236" spans="1:13">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11706,8 +11825,8 @@
       <c r="F236">
         <v>6289515692970</v>
       </c>
-      <c r="G236">
-        <v>1.2E-16</v>
+      <c r="G236" s="1" t="s">
+        <v>1813</v>
       </c>
       <c r="J236" t="s">
         <v>15</v>
@@ -11719,7 +11838,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="237" spans="1:13">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11732,8 +11851,8 @@
       <c r="F237">
         <v>628123561562</v>
       </c>
-      <c r="G237">
-        <v>1.2E-17</v>
+      <c r="G237" s="1" t="s">
+        <v>1814</v>
       </c>
       <c r="J237" t="s">
         <v>15</v>
@@ -11745,7 +11864,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="238" spans="1:13">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11758,8 +11877,8 @@
       <c r="F238">
         <v>628114500332</v>
       </c>
-      <c r="G238">
-        <v>1.2E-18</v>
+      <c r="G238" s="1" t="s">
+        <v>1815</v>
       </c>
       <c r="J238" t="s">
         <v>15</v>
@@ -11771,7 +11890,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11784,8 +11903,8 @@
       <c r="F239">
         <v>6285732999448</v>
       </c>
-      <c r="G239">
-        <v>1.2E-19</v>
+      <c r="G239" s="1" t="s">
+        <v>1816</v>
       </c>
       <c r="J239" t="s">
         <v>15</v>
@@ -11797,7 +11916,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="240" spans="1:13">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11810,8 +11929,8 @@
       <c r="F240">
         <v>6282142892699</v>
       </c>
-      <c r="G240">
-        <v>1.2E-20</v>
+      <c r="G240" s="1" t="s">
+        <v>1817</v>
       </c>
       <c r="J240" t="s">
         <v>15</v>
@@ -11823,7 +11942,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="241" spans="1:13">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11836,8 +11955,8 @@
       <c r="F241">
         <v>6289506615606</v>
       </c>
-      <c r="G241">
-        <v>1.2E-21</v>
+      <c r="G241" s="1" t="s">
+        <v>1818</v>
       </c>
       <c r="J241" t="s">
         <v>15</v>
@@ -11849,7 +11968,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11862,8 +11981,8 @@
       <c r="F242">
         <v>6289691964105</v>
       </c>
-      <c r="G242">
-        <v>1.2E-22</v>
+      <c r="G242" s="1" t="s">
+        <v>1819</v>
       </c>
       <c r="J242" t="s">
         <v>15</v>
@@ -11875,7 +11994,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="243" spans="1:13">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11888,8 +12007,8 @@
       <c r="F243">
         <v>6281335126094</v>
       </c>
-      <c r="G243">
-        <v>1.2E-23</v>
+      <c r="G243" s="1" t="s">
+        <v>1820</v>
       </c>
       <c r="J243" t="s">
         <v>15</v>
@@ -11901,7 +12020,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="244" spans="1:13">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11914,8 +12033,8 @@
       <c r="F244">
         <v>628113008411</v>
       </c>
-      <c r="G244">
-        <v>1.2E-24</v>
+      <c r="G244" s="1" t="s">
+        <v>1821</v>
       </c>
       <c r="J244" t="s">
         <v>15</v>
@@ -11927,7 +12046,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="245" spans="1:13">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11940,8 +12059,8 @@
       <c r="F245">
         <v>6282247622109</v>
       </c>
-      <c r="G245">
-        <v>1.2E-25</v>
+      <c r="G245" s="1" t="s">
+        <v>1822</v>
       </c>
       <c r="J245" t="s">
         <v>15</v>
@@ -11953,7 +12072,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="246" spans="1:13">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11966,8 +12085,8 @@
       <c r="F246">
         <v>6285858888011</v>
       </c>
-      <c r="G246">
-        <v>1.2E-26</v>
+      <c r="G246" s="1" t="s">
+        <v>1823</v>
       </c>
       <c r="J246" t="s">
         <v>15</v>
@@ -11979,7 +12098,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="247" spans="1:13">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11992,8 +12111,8 @@
       <c r="F247">
         <v>6281931435856</v>
       </c>
-      <c r="G247">
-        <v>1.2E-27</v>
+      <c r="G247" s="1" t="s">
+        <v>1824</v>
       </c>
       <c r="J247" t="s">
         <v>15</v>
@@ -12005,7 +12124,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="248" spans="1:13">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -12018,8 +12137,8 @@
       <c r="F248">
         <v>628114803123</v>
       </c>
-      <c r="G248">
-        <v>1.2E-28</v>
+      <c r="G248" s="1" t="s">
+        <v>1825</v>
       </c>
       <c r="J248" t="s">
         <v>15</v>
@@ -12031,7 +12150,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -12044,8 +12163,8 @@
       <c r="F249">
         <v>6281358954498</v>
       </c>
-      <c r="G249">
-        <v>1.2E-29</v>
+      <c r="G249" s="1" t="s">
+        <v>1826</v>
       </c>
       <c r="J249" t="s">
         <v>15</v>
@@ -12057,7 +12176,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -12070,8 +12189,8 @@
       <c r="F250">
         <v>6281247880690</v>
       </c>
-      <c r="G250">
-        <v>1.2E-30</v>
+      <c r="G250" s="1" t="s">
+        <v>1827</v>
       </c>
       <c r="J250" t="s">
         <v>15</v>
@@ -12083,7 +12202,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="251" spans="1:13">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -12096,8 +12215,8 @@
       <c r="F251">
         <v>6282334314822</v>
       </c>
-      <c r="G251">
-        <v>1.2E-31</v>
+      <c r="G251" s="1" t="s">
+        <v>1828</v>
       </c>
       <c r="J251" t="s">
         <v>15</v>
@@ -12109,7 +12228,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="252" spans="1:13">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -12135,7 +12254,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -12161,7 +12280,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="254" spans="1:13">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -12187,7 +12306,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -12213,7 +12332,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -12239,7 +12358,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="257" spans="1:13">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -12265,7 +12384,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="258" spans="1:13">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -12291,7 +12410,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="259" spans="1:13">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -12317,7 +12436,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -12343,7 +12462,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="261" spans="1:13">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -12369,7 +12488,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -12395,7 +12514,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="263" spans="1:13">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -12421,7 +12540,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="264" spans="1:13">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -12447,7 +12566,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="265" spans="1:13">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -12473,7 +12592,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="266" spans="1:13">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -12499,7 +12618,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="267" spans="1:13">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -12525,7 +12644,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="268" spans="1:13">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -12551,7 +12670,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="269" spans="1:13">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -12577,7 +12696,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="270" spans="1:13">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -12603,7 +12722,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="271" spans="1:13">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -12629,7 +12748,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="272" spans="1:13">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -12655,7 +12774,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="273" spans="1:13">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -12684,7 +12803,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="274" spans="1:13">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -12710,7 +12829,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="275" spans="1:13">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -12736,7 +12855,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="276" spans="1:13">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -12762,7 +12881,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="277" spans="1:13">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -12788,7 +12907,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="278" spans="1:13">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -12814,7 +12933,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="279" spans="1:13">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -12843,7 +12962,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="280" spans="1:13">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -12869,7 +12988,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="281" spans="1:13">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -12895,7 +13014,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="282" spans="1:13">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -12921,7 +13040,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="283" spans="1:13">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -12947,7 +13066,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -12976,7 +13095,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="285" spans="1:13">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -13002,7 +13121,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="286" spans="1:13">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -13028,7 +13147,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="287" spans="1:13">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -13054,7 +13173,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="288" spans="1:13">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -13080,7 +13199,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="289" spans="1:13">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -13106,7 +13225,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="290" spans="1:13">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -13132,7 +13251,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="291" spans="1:13">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -13158,7 +13277,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="292" spans="1:13">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -13184,7 +13303,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="293" spans="1:13">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -13210,7 +13329,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="294" spans="1:13">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -13239,7 +13358,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="295" spans="1:13">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -13265,7 +13384,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="296" spans="1:13">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -13294,7 +13413,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="297" spans="1:13">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -13320,7 +13439,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="298" spans="1:13">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -13346,7 +13465,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="299" spans="1:13">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -13372,7 +13491,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="300" spans="1:13">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -13398,7 +13517,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="301" spans="1:13">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -13424,7 +13543,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="302" spans="1:13">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -13450,7 +13569,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="303" spans="1:13">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -13476,7 +13595,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="304" spans="1:13">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -13502,7 +13621,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="305" spans="1:13">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -13528,7 +13647,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="306" spans="1:13">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -13554,7 +13673,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="307" spans="1:13">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -13580,7 +13699,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="308" spans="1:13">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -13606,7 +13725,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="309" spans="1:13">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -13632,7 +13751,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="310" spans="1:13">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -13658,7 +13777,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="311" spans="1:13">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -13684,7 +13803,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="312" spans="1:13">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -13710,7 +13829,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="313" spans="1:13">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -13736,7 +13855,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="314" spans="1:13">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -13762,7 +13881,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="315" spans="1:13">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -13788,7 +13907,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="316" spans="1:13">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -13814,7 +13933,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="317" spans="1:13">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -13843,7 +13962,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="318" spans="1:13">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -13869,7 +13988,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="319" spans="1:13">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -13895,7 +14014,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="320" spans="1:13">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -13921,7 +14040,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="321" spans="1:13">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -13947,7 +14066,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="322" spans="1:13">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -13973,7 +14092,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="323" spans="1:13">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -13999,7 +14118,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="324" spans="1:13">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -14025,7 +14144,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="325" spans="1:13">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -14051,7 +14170,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="326" spans="1:13">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -14077,7 +14196,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="327" spans="1:13">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -14103,7 +14222,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="328" spans="1:13">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -14129,7 +14248,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="329" spans="1:13">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -14155,7 +14274,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="330" spans="1:13">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -14181,7 +14300,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="331" spans="1:13">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -14210,7 +14329,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="332" spans="1:13">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -14236,7 +14355,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="333" spans="1:13">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -14262,7 +14381,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="334" spans="1:13">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -14288,7 +14407,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="335" spans="1:13">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -14314,7 +14433,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="336" spans="1:13">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -14340,7 +14459,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="337" spans="1:13">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -14366,7 +14485,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="338" spans="1:13">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -14392,7 +14511,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="339" spans="1:13">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -14418,7 +14537,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="340" spans="1:13">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -14444,7 +14563,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="341" spans="1:13">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -14470,7 +14589,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="342" spans="1:13">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>341</v>
       </c>
@@ -14499,7 +14618,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="343" spans="1:13">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -14525,7 +14644,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="344" spans="1:13">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>343</v>
       </c>
@@ -14551,7 +14670,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="345" spans="1:13">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>344</v>
       </c>
@@ -14577,7 +14696,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="346" spans="1:13">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>345</v>
       </c>
@@ -14606,7 +14725,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="347" spans="1:13">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -14632,7 +14751,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="348" spans="1:13">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>347</v>
       </c>
@@ -14658,7 +14777,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="349" spans="1:13">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -14684,7 +14803,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="350" spans="1:13">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -14710,7 +14829,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="351" spans="1:13">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -14736,7 +14855,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="352" spans="1:13">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>351</v>
       </c>
@@ -14762,7 +14881,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="353" spans="1:13">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -14788,7 +14907,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="354" spans="1:13">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>353</v>
       </c>
@@ -14814,7 +14933,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="355" spans="1:13">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -14840,7 +14959,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="356" spans="1:13">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>355</v>
       </c>
@@ -14866,7 +14985,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="357" spans="1:13">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>356</v>
       </c>
@@ -14892,7 +15011,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="358" spans="1:13">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>357</v>
       </c>
@@ -14918,7 +15037,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="359" spans="1:13">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -14944,7 +15063,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="360" spans="1:13">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -14970,7 +15089,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="361" spans="1:13">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>360</v>
       </c>
@@ -14996,7 +15115,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="362" spans="1:13">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -15022,7 +15141,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="363" spans="1:13">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>362</v>
       </c>
@@ -15048,7 +15167,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="364" spans="1:13">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -15077,7 +15196,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="365" spans="1:13">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -15103,7 +15222,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="366" spans="1:13">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -15129,7 +15248,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="367" spans="1:13">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>366</v>
       </c>
@@ -15155,7 +15274,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="368" spans="1:13">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -15181,7 +15300,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="369" spans="1:13">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -15207,7 +15326,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="370" spans="1:13">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -15233,7 +15352,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="371" spans="1:13">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -15262,7 +15381,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="372" spans="1:13">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -15288,7 +15407,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="373" spans="1:13">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>372</v>
       </c>
@@ -15314,7 +15433,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="374" spans="1:13">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>373</v>
       </c>
@@ -15340,7 +15459,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="375" spans="1:13">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>374</v>
       </c>
@@ -15369,7 +15488,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="376" spans="1:13">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>375</v>
       </c>
@@ -15395,7 +15514,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="377" spans="1:13">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>376</v>
       </c>
@@ -15421,7 +15540,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="378" spans="1:13">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>377</v>
       </c>
@@ -15447,7 +15566,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="379" spans="1:13">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>378</v>
       </c>
@@ -15473,7 +15592,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="380" spans="1:13">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>379</v>
       </c>
@@ -15499,7 +15618,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="381" spans="1:13">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -15525,7 +15644,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="382" spans="1:13">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -15551,7 +15670,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="383" spans="1:13">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -15577,7 +15696,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="384" spans="1:13">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -15603,7 +15722,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="385" spans="1:13">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -15629,7 +15748,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="386" spans="1:13">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>385</v>
       </c>
@@ -15655,7 +15774,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="387" spans="1:13">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>386</v>
       </c>
@@ -15681,7 +15800,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="388" spans="1:13">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>387</v>
       </c>
@@ -15707,7 +15826,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -15733,7 +15852,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="390" spans="1:13">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -15759,7 +15878,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="391" spans="1:13">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -15785,7 +15904,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="392" spans="1:13">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -15811,7 +15930,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="393" spans="1:13">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -15837,7 +15956,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="394" spans="1:13">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>393</v>
       </c>
@@ -15863,7 +15982,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="395" spans="1:13">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -15889,7 +16008,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="396" spans="1:13">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>395</v>
       </c>
@@ -15915,7 +16034,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="397" spans="1:13">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -15941,7 +16060,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="398" spans="1:13">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -15970,7 +16089,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="399" spans="1:13">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -15996,7 +16115,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="400" spans="1:13">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -16022,7 +16141,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="401" spans="1:13">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -16048,7 +16167,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="402" spans="1:13">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -16074,7 +16193,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="403" spans="1:13">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>402</v>
       </c>
@@ -16100,7 +16219,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="404" spans="1:13">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>403</v>
       </c>
@@ -16126,7 +16245,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="405" spans="1:13">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -16155,7 +16274,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="406" spans="1:13">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -16184,7 +16303,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="407" spans="1:13">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -16210,7 +16329,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="408" spans="1:13">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>407</v>
       </c>
@@ -16236,7 +16355,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="409" spans="1:13">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -16262,7 +16381,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="410" spans="1:13">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>409</v>
       </c>
@@ -16288,7 +16407,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="411" spans="1:13">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>410</v>
       </c>
@@ -16314,7 +16433,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="412" spans="1:13">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -16340,7 +16459,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="413" spans="1:13">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>412</v>
       </c>
@@ -16366,7 +16485,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="414" spans="1:13">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -16392,7 +16511,7 @@
         <v>1589</v>
       </c>
     </row>
-    <row r="415" spans="1:13">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -16418,7 +16537,7 @@
         <v>1593</v>
       </c>
     </row>
-    <row r="416" spans="1:13">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>415</v>
       </c>
@@ -16444,7 +16563,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="417" spans="1:13">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -16470,7 +16589,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="418" spans="1:13">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>417</v>
       </c>
@@ -16496,7 +16615,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="419" spans="1:13">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>418</v>
       </c>
@@ -16522,7 +16641,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="420" spans="1:13">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>419</v>
       </c>
@@ -16551,7 +16670,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="421" spans="1:13">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>420</v>
       </c>
@@ -16577,7 +16696,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="422" spans="1:13">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>421</v>
       </c>
@@ -16603,7 +16722,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="423" spans="1:13">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>422</v>
       </c>
@@ -16629,7 +16748,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="424" spans="1:13">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>423</v>
       </c>
@@ -16655,7 +16774,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="425" spans="1:13">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>424</v>
       </c>
@@ -16681,7 +16800,7 @@
         <v>1634</v>
       </c>
     </row>
-    <row r="426" spans="1:13">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>425</v>
       </c>
@@ -16707,7 +16826,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="427" spans="1:13">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>426</v>
       </c>
@@ -16733,7 +16852,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="428" spans="1:13">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>427</v>
       </c>
@@ -16762,7 +16881,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="429" spans="1:13">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>428</v>
       </c>
@@ -16791,7 +16910,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="430" spans="1:13">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -16817,7 +16936,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="431" spans="1:13">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>430</v>
       </c>
@@ -16843,7 +16962,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="432" spans="1:13">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>431</v>
       </c>
@@ -16872,7 +16991,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="433" spans="1:13">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>432</v>
       </c>
@@ -16898,7 +17017,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="434" spans="1:13">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>433</v>
       </c>
@@ -16924,7 +17043,7 @@
         <v>1673</v>
       </c>
     </row>
-    <row r="435" spans="1:13">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>434</v>
       </c>
@@ -16953,7 +17072,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="436" spans="1:13">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>435</v>
       </c>
@@ -16979,7 +17098,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="437" spans="1:13">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>436</v>
       </c>
@@ -17005,7 +17124,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="438" spans="1:13">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>437</v>
       </c>
@@ -17031,7 +17150,7 @@
         <v>1690</v>
       </c>
     </row>
-    <row r="439" spans="1:13">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>438</v>
       </c>
@@ -17060,7 +17179,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="440" spans="1:13">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>439</v>
       </c>
@@ -17086,7 +17205,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="441" spans="1:13">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>440</v>
       </c>
@@ -17112,7 +17231,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="442" spans="1:13">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>441</v>
       </c>
@@ -17138,7 +17257,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="443" spans="1:13">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>442</v>
       </c>
@@ -17164,7 +17283,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="444" spans="1:13">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>443</v>
       </c>
@@ -17190,7 +17309,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="445" spans="1:13">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>444</v>
       </c>
@@ -17216,7 +17335,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="446" spans="1:13">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>445</v>
       </c>
@@ -17242,7 +17361,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="447" spans="1:13">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>446</v>
       </c>
@@ -17271,7 +17390,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="448" spans="1:13">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>447</v>
       </c>
@@ -17297,7 +17416,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="449" spans="1:13">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>448</v>
       </c>
@@ -17323,7 +17442,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="450" spans="1:13">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>449</v>
       </c>
@@ -17349,7 +17468,7 @@
         <v>1739</v>
       </c>
     </row>
-    <row r="451" spans="1:13">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>450</v>
       </c>
@@ -17375,7 +17494,7 @@
         <v>1743</v>
       </c>
     </row>
-    <row r="452" spans="1:13">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>451</v>
       </c>
@@ -17401,7 +17520,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="453" spans="1:13">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>452</v>
       </c>
@@ -17427,7 +17546,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="454" spans="1:13">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>453</v>
       </c>
@@ -17453,7 +17572,7 @@
         <v>1755</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>454</v>
       </c>
@@ -17479,7 +17598,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="456" spans="1:13">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>455</v>
       </c>
@@ -17505,7 +17624,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>456</v>
       </c>
@@ -17531,7 +17650,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="458" spans="1:13">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>457</v>
       </c>
@@ -17557,7 +17676,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="459" spans="1:13">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>458</v>
       </c>
@@ -17583,7 +17702,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="460" spans="1:13">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>459</v>
       </c>
@@ -17612,7 +17731,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="461" spans="1:13">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>460</v>
       </c>
@@ -17638,7 +17757,7 @@
         <v>1784</v>
       </c>
     </row>
-    <row r="462" spans="1:13">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>461</v>
       </c>
@@ -17664,7 +17783,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>462</v>
       </c>
@@ -17693,7 +17812,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="464" spans="1:13">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>463</v>
       </c>
@@ -17720,17 +17839,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>
--- a/reportstellarsoiree.xlsx
+++ b/reportstellarsoiree.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TABITA\Hwa Ind Prom\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F235EA40-A73C-4D25-AF92-6D5A38CF0671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{067FECF8-0C28-954A-B5BC-8965D0D0802F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191028" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2292" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1471">
   <si>
     <t>No</t>
   </si>
@@ -4437,6 +4437,12 @@
   </si>
   <si>
     <t>12L</t>
+  </si>
+  <si>
+    <t>OSIS</t>
+  </si>
+  <si>
+    <t>GURU DAN STAFF</t>
   </si>
 </sst>
 </file>
@@ -4782,9 +4788,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M464"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4825,7 +4831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4838,6 +4844,9 @@
       <c r="F2">
         <v>628170470382</v>
       </c>
+      <c r="G2" t="s">
+        <v>1469</v>
+      </c>
       <c r="J2" t="s">
         <v>15</v>
       </c>
@@ -4851,7 +4860,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4864,6 +4873,9 @@
       <c r="F3">
         <v>6281818137383</v>
       </c>
+      <c r="G3" t="s">
+        <v>1469</v>
+      </c>
       <c r="J3" t="s">
         <v>15</v>
       </c>
@@ -4877,7 +4889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4890,6 +4902,9 @@
       <c r="F4">
         <v>6281336691764</v>
       </c>
+      <c r="G4" t="s">
+        <v>1469</v>
+      </c>
       <c r="J4" t="s">
         <v>15</v>
       </c>
@@ -4900,7 +4915,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4913,6 +4928,9 @@
       <c r="F5">
         <v>628179602997</v>
       </c>
+      <c r="G5" t="s">
+        <v>1469</v>
+      </c>
       <c r="J5" t="s">
         <v>15</v>
       </c>
@@ -4923,7 +4941,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4936,6 +4954,9 @@
       <c r="F6">
         <v>6285649927363</v>
       </c>
+      <c r="G6" t="s">
+        <v>1469</v>
+      </c>
       <c r="J6" t="s">
         <v>15</v>
       </c>
@@ -4946,7 +4967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4959,6 +4980,9 @@
       <c r="F7">
         <v>6281334792770</v>
       </c>
+      <c r="G7" t="s">
+        <v>1469</v>
+      </c>
       <c r="J7" t="s">
         <v>15</v>
       </c>
@@ -4972,7 +4996,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4985,6 +5009,9 @@
       <c r="F8">
         <v>6282257634886</v>
       </c>
+      <c r="G8" t="s">
+        <v>1469</v>
+      </c>
       <c r="J8" t="s">
         <v>15</v>
       </c>
@@ -4995,7 +5022,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5008,6 +5035,9 @@
       <c r="F9">
         <v>6281334151569</v>
       </c>
+      <c r="G9" t="s">
+        <v>1469</v>
+      </c>
       <c r="J9" t="s">
         <v>15</v>
       </c>
@@ -5018,7 +5048,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5031,6 +5061,9 @@
       <c r="F10">
         <v>6281334450055</v>
       </c>
+      <c r="G10" t="s">
+        <v>1469</v>
+      </c>
       <c r="J10" t="s">
         <v>43</v>
       </c>
@@ -5041,7 +5074,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5054,6 +5087,9 @@
       <c r="F11">
         <v>628179603425</v>
       </c>
+      <c r="G11" t="s">
+        <v>1469</v>
+      </c>
       <c r="J11" t="s">
         <v>15</v>
       </c>
@@ -5064,7 +5100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5077,6 +5113,9 @@
       <c r="F12">
         <v>6282139666128</v>
       </c>
+      <c r="G12" t="s">
+        <v>1469</v>
+      </c>
       <c r="J12" t="s">
         <v>15</v>
       </c>
@@ -5087,7 +5126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5100,6 +5139,9 @@
       <c r="F13">
         <v>628175406785</v>
       </c>
+      <c r="G13" t="s">
+        <v>1469</v>
+      </c>
       <c r="J13" t="s">
         <v>15</v>
       </c>
@@ -5110,7 +5152,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5123,6 +5165,9 @@
       <c r="F14">
         <v>6282148341873</v>
       </c>
+      <c r="G14" t="s">
+        <v>1469</v>
+      </c>
       <c r="J14" t="s">
         <v>43</v>
       </c>
@@ -5133,7 +5178,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5146,6 +5191,9 @@
       <c r="F15">
         <v>6281332050819</v>
       </c>
+      <c r="G15" t="s">
+        <v>1469</v>
+      </c>
       <c r="J15" t="s">
         <v>15</v>
       </c>
@@ -5159,7 +5207,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5172,6 +5220,9 @@
       <c r="F16">
         <v>628123387337</v>
       </c>
+      <c r="G16" t="s">
+        <v>1469</v>
+      </c>
       <c r="J16" t="s">
         <v>15</v>
       </c>
@@ -5182,7 +5233,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5195,6 +5246,9 @@
       <c r="F17">
         <v>6282139896030</v>
       </c>
+      <c r="G17" t="s">
+        <v>1469</v>
+      </c>
       <c r="J17" t="s">
         <v>15</v>
       </c>
@@ -5205,7 +5259,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5218,6 +5272,9 @@
       <c r="F18">
         <v>6281937799024</v>
       </c>
+      <c r="G18" t="s">
+        <v>1469</v>
+      </c>
       <c r="J18" t="s">
         <v>15</v>
       </c>
@@ -5228,7 +5285,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5241,6 +5298,9 @@
       <c r="F19">
         <v>6285156164955</v>
       </c>
+      <c r="G19" t="s">
+        <v>1469</v>
+      </c>
       <c r="J19" t="s">
         <v>43</v>
       </c>
@@ -5251,7 +5311,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5264,6 +5324,9 @@
       <c r="F20">
         <v>628155511298</v>
       </c>
+      <c r="G20" t="s">
+        <v>1469</v>
+      </c>
       <c r="J20" t="s">
         <v>15</v>
       </c>
@@ -5274,7 +5337,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5287,6 +5350,9 @@
       <c r="F21">
         <v>6285790863015</v>
       </c>
+      <c r="G21" t="s">
+        <v>1469</v>
+      </c>
       <c r="J21" t="s">
         <v>15</v>
       </c>
@@ -5297,7 +5363,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5310,6 +5376,9 @@
       <c r="F22">
         <v>6282331819313</v>
       </c>
+      <c r="G22" t="s">
+        <v>1469</v>
+      </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
@@ -5323,7 +5392,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5336,6 +5405,9 @@
       <c r="F23">
         <v>6281334112615</v>
       </c>
+      <c r="G23" t="s">
+        <v>1469</v>
+      </c>
       <c r="J23" t="s">
         <v>15</v>
       </c>
@@ -5346,7 +5418,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5359,6 +5431,9 @@
       <c r="F24">
         <v>6281334212626</v>
       </c>
+      <c r="G24" t="s">
+        <v>1469</v>
+      </c>
       <c r="J24" t="s">
         <v>15</v>
       </c>
@@ -5372,7 +5447,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5385,6 +5460,9 @@
       <c r="F25">
         <v>6281335839249</v>
       </c>
+      <c r="G25" t="s">
+        <v>1469</v>
+      </c>
       <c r="J25" t="s">
         <v>15</v>
       </c>
@@ -5395,7 +5473,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5408,6 +5486,9 @@
       <c r="F26">
         <v>6283848050976</v>
       </c>
+      <c r="G26" t="s">
+        <v>1469</v>
+      </c>
       <c r="J26" t="s">
         <v>15</v>
       </c>
@@ -5418,7 +5499,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5431,6 +5512,9 @@
       <c r="F27">
         <v>6281252702510</v>
       </c>
+      <c r="G27" t="s">
+        <v>1469</v>
+      </c>
       <c r="J27" t="s">
         <v>15</v>
       </c>
@@ -5444,7 +5528,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5457,6 +5541,9 @@
       <c r="F28">
         <v>628563568740</v>
       </c>
+      <c r="G28" t="s">
+        <v>1469</v>
+      </c>
       <c r="J28" t="s">
         <v>43</v>
       </c>
@@ -5467,7 +5554,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5480,6 +5567,9 @@
       <c r="F29">
         <v>6281331399677</v>
       </c>
+      <c r="G29" t="s">
+        <v>1469</v>
+      </c>
       <c r="J29" t="s">
         <v>15</v>
       </c>
@@ -5490,7 +5580,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5503,6 +5593,9 @@
       <c r="F30">
         <v>6281334056650</v>
       </c>
+      <c r="G30" t="s">
+        <v>1469</v>
+      </c>
       <c r="J30" t="s">
         <v>15</v>
       </c>
@@ -5516,7 +5609,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5529,6 +5622,9 @@
       <c r="F31">
         <v>6287701681982</v>
       </c>
+      <c r="G31" t="s">
+        <v>1469</v>
+      </c>
       <c r="J31" t="s">
         <v>15</v>
       </c>
@@ -5542,7 +5638,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5555,6 +5651,9 @@
       <c r="F32">
         <v>6281333400088</v>
       </c>
+      <c r="G32" t="s">
+        <v>1469</v>
+      </c>
       <c r="J32" t="s">
         <v>15</v>
       </c>
@@ -5568,7 +5667,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5581,6 +5680,9 @@
       <c r="F33">
         <v>6285755700531</v>
       </c>
+      <c r="G33" t="s">
+        <v>1469</v>
+      </c>
       <c r="J33" t="s">
         <v>15</v>
       </c>
@@ -5591,7 +5693,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5604,6 +5706,9 @@
       <c r="F34">
         <v>628562813537</v>
       </c>
+      <c r="G34" t="s">
+        <v>1469</v>
+      </c>
       <c r="J34" t="s">
         <v>123</v>
       </c>
@@ -5617,7 +5722,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5630,6 +5735,9 @@
       <c r="F35">
         <v>6281232056437</v>
       </c>
+      <c r="G35" t="s">
+        <v>1469</v>
+      </c>
       <c r="J35" t="s">
         <v>15</v>
       </c>
@@ -5640,7 +5748,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5653,6 +5761,9 @@
       <c r="F36">
         <v>6285643864321</v>
       </c>
+      <c r="G36" t="s">
+        <v>1469</v>
+      </c>
       <c r="J36" t="s">
         <v>15</v>
       </c>
@@ -5663,7 +5774,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5676,6 +5787,9 @@
       <c r="F37">
         <v>6281937778708</v>
       </c>
+      <c r="G37" t="s">
+        <v>1469</v>
+      </c>
       <c r="J37" t="s">
         <v>15</v>
       </c>
@@ -5686,7 +5800,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5699,6 +5813,9 @@
       <c r="F38">
         <v>6285707636369</v>
       </c>
+      <c r="G38" t="s">
+        <v>1469</v>
+      </c>
       <c r="J38" t="s">
         <v>15</v>
       </c>
@@ -5709,7 +5826,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5722,6 +5839,9 @@
       <c r="F39">
         <v>6281555767329</v>
       </c>
+      <c r="G39" t="s">
+        <v>1469</v>
+      </c>
       <c r="J39" t="s">
         <v>15</v>
       </c>
@@ -5732,7 +5852,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5745,6 +5865,9 @@
       <c r="F40">
         <v>6282233979952</v>
       </c>
+      <c r="G40" t="s">
+        <v>1469</v>
+      </c>
       <c r="J40" t="s">
         <v>15</v>
       </c>
@@ -5755,7 +5878,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5768,6 +5891,9 @@
       <c r="F41">
         <v>6282131726070</v>
       </c>
+      <c r="G41" t="s">
+        <v>1469</v>
+      </c>
       <c r="J41" t="s">
         <v>15</v>
       </c>
@@ -5778,7 +5904,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5791,6 +5917,9 @@
       <c r="F42">
         <v>6287859887587</v>
       </c>
+      <c r="G42" t="s">
+        <v>1469</v>
+      </c>
       <c r="J42" t="s">
         <v>123</v>
       </c>
@@ -5804,7 +5933,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5817,6 +5946,9 @@
       <c r="F43">
         <v>6285257601040</v>
       </c>
+      <c r="G43" t="s">
+        <v>1469</v>
+      </c>
       <c r="J43" t="s">
         <v>15</v>
       </c>
@@ -5830,7 +5962,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5843,6 +5975,9 @@
       <c r="F44">
         <v>6281515392119</v>
       </c>
+      <c r="G44" t="s">
+        <v>1469</v>
+      </c>
       <c r="J44" t="s">
         <v>15</v>
       </c>
@@ -5853,7 +5988,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5866,6 +6001,9 @@
       <c r="F45">
         <v>6285933051018</v>
       </c>
+      <c r="G45" t="s">
+        <v>1469</v>
+      </c>
       <c r="J45" t="s">
         <v>15</v>
       </c>
@@ -5879,7 +6017,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5892,6 +6030,9 @@
       <c r="F46">
         <v>6281233516737</v>
       </c>
+      <c r="G46" t="s">
+        <v>1469</v>
+      </c>
       <c r="J46" t="s">
         <v>15</v>
       </c>
@@ -5902,7 +6043,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5915,6 +6056,9 @@
       <c r="F47">
         <v>6281216131689</v>
       </c>
+      <c r="G47" t="s">
+        <v>1469</v>
+      </c>
       <c r="J47" t="s">
         <v>15</v>
       </c>
@@ -5925,7 +6069,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5938,6 +6082,9 @@
       <c r="F48">
         <v>6285331391901</v>
       </c>
+      <c r="G48" t="s">
+        <v>1469</v>
+      </c>
       <c r="J48" t="s">
         <v>15</v>
       </c>
@@ -5948,7 +6095,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5961,6 +6108,9 @@
       <c r="F49">
         <v>6281233553418</v>
       </c>
+      <c r="G49" t="s">
+        <v>1469</v>
+      </c>
       <c r="J49" t="s">
         <v>15</v>
       </c>
@@ -5971,7 +6121,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5984,6 +6134,9 @@
       <c r="F50">
         <v>6281210849961</v>
       </c>
+      <c r="G50" t="s">
+        <v>1469</v>
+      </c>
       <c r="J50" t="s">
         <v>123</v>
       </c>
@@ -5997,7 +6150,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6010,6 +6163,9 @@
       <c r="F51">
         <v>6289660460697</v>
       </c>
+      <c r="G51" t="s">
+        <v>1469</v>
+      </c>
       <c r="J51" t="s">
         <v>15</v>
       </c>
@@ -6020,7 +6176,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6033,6 +6189,9 @@
       <c r="F52">
         <v>6281217242048</v>
       </c>
+      <c r="G52" t="s">
+        <v>1469</v>
+      </c>
       <c r="J52" t="s">
         <v>15</v>
       </c>
@@ -6043,7 +6202,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6056,6 +6215,9 @@
       <c r="F53">
         <v>6281252439951</v>
       </c>
+      <c r="G53" t="s">
+        <v>1469</v>
+      </c>
       <c r="J53" t="s">
         <v>15</v>
       </c>
@@ -6066,7 +6228,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6079,6 +6241,9 @@
       <c r="F54">
         <v>62818538879</v>
       </c>
+      <c r="G54" t="s">
+        <v>1469</v>
+      </c>
       <c r="J54" t="s">
         <v>15</v>
       </c>
@@ -6089,7 +6254,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6102,6 +6267,9 @@
       <c r="F55">
         <v>6283867272006</v>
       </c>
+      <c r="G55" t="s">
+        <v>1469</v>
+      </c>
       <c r="J55" t="s">
         <v>15</v>
       </c>
@@ -6112,7 +6280,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6125,6 +6293,9 @@
       <c r="F56">
         <v>6281230694246</v>
       </c>
+      <c r="G56" t="s">
+        <v>1469</v>
+      </c>
       <c r="J56" t="s">
         <v>15</v>
       </c>
@@ -6135,7 +6306,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6148,6 +6319,9 @@
       <c r="F57">
         <v>6285701521177</v>
       </c>
+      <c r="G57" t="s">
+        <v>1469</v>
+      </c>
       <c r="J57" t="s">
         <v>15</v>
       </c>
@@ -6158,7 +6332,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6171,6 +6345,9 @@
       <c r="F58">
         <v>628125225789</v>
       </c>
+      <c r="G58" t="s">
+        <v>1469</v>
+      </c>
       <c r="J58" t="s">
         <v>43</v>
       </c>
@@ -6181,7 +6358,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6194,6 +6371,9 @@
       <c r="F59">
         <v>6281336691763</v>
       </c>
+      <c r="G59" t="s">
+        <v>1469</v>
+      </c>
       <c r="J59" t="s">
         <v>15</v>
       </c>
@@ -6207,7 +6387,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6220,6 +6400,9 @@
       <c r="F60">
         <v>6282232323043</v>
       </c>
+      <c r="G60" t="s">
+        <v>1469</v>
+      </c>
       <c r="J60" t="s">
         <v>15</v>
       </c>
@@ -6230,7 +6413,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6243,6 +6426,9 @@
       <c r="F61">
         <v>6281934991711</v>
       </c>
+      <c r="G61" t="s">
+        <v>1469</v>
+      </c>
       <c r="J61" t="s">
         <v>15</v>
       </c>
@@ -6253,7 +6439,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6266,6 +6452,9 @@
       <c r="F62">
         <v>6287859101907</v>
       </c>
+      <c r="G62" t="s">
+        <v>1469</v>
+      </c>
       <c r="J62" t="s">
         <v>15</v>
       </c>
@@ -6276,7 +6465,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6289,6 +6478,9 @@
       <c r="F63">
         <v>6285855480996</v>
       </c>
+      <c r="G63" t="s">
+        <v>1469</v>
+      </c>
       <c r="J63" t="s">
         <v>15</v>
       </c>
@@ -6299,7 +6491,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6312,6 +6504,9 @@
       <c r="F64">
         <v>6281806020894</v>
       </c>
+      <c r="G64" t="s">
+        <v>1469</v>
+      </c>
       <c r="J64" t="s">
         <v>15</v>
       </c>
@@ -6322,7 +6517,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6335,6 +6530,9 @@
       <c r="F65">
         <v>6281230153626</v>
       </c>
+      <c r="G65" t="s">
+        <v>1469</v>
+      </c>
       <c r="J65" t="s">
         <v>15</v>
       </c>
@@ -6348,7 +6546,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6361,6 +6559,9 @@
       <c r="F66">
         <v>6283869682827</v>
       </c>
+      <c r="G66" t="s">
+        <v>1469</v>
+      </c>
       <c r="J66" t="s">
         <v>123</v>
       </c>
@@ -6371,7 +6572,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6384,6 +6585,9 @@
       <c r="F67">
         <v>6281250172072</v>
       </c>
+      <c r="G67" t="s">
+        <v>1469</v>
+      </c>
       <c r="J67" t="s">
         <v>15</v>
       </c>
@@ -6394,7 +6598,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6407,6 +6611,9 @@
       <c r="F68">
         <v>6282112194857</v>
       </c>
+      <c r="G68" t="s">
+        <v>1469</v>
+      </c>
       <c r="J68" t="s">
         <v>15</v>
       </c>
@@ -6417,7 +6624,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6430,6 +6637,9 @@
       <c r="F69">
         <v>6282136444169</v>
       </c>
+      <c r="G69" t="s">
+        <v>1469</v>
+      </c>
       <c r="J69" t="s">
         <v>15</v>
       </c>
@@ -6440,7 +6650,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6453,6 +6663,9 @@
       <c r="F70">
         <v>6281555648210</v>
       </c>
+      <c r="G70" t="s">
+        <v>1469</v>
+      </c>
       <c r="J70" t="s">
         <v>15</v>
       </c>
@@ -6466,7 +6679,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6479,6 +6692,9 @@
       <c r="F71">
         <v>6281252324420</v>
       </c>
+      <c r="G71" t="s">
+        <v>1469</v>
+      </c>
       <c r="J71" t="s">
         <v>15</v>
       </c>
@@ -6489,7 +6705,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6502,6 +6718,9 @@
       <c r="F72">
         <v>62816558122</v>
       </c>
+      <c r="G72" t="s">
+        <v>1469</v>
+      </c>
       <c r="J72" t="s">
         <v>123</v>
       </c>
@@ -6512,7 +6731,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6525,6 +6744,9 @@
       <c r="F73">
         <v>6281233294669</v>
       </c>
+      <c r="G73" t="s">
+        <v>1469</v>
+      </c>
       <c r="J73" t="s">
         <v>15</v>
       </c>
@@ -6535,7 +6757,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6548,6 +6770,9 @@
       <c r="F74">
         <v>62818384463</v>
       </c>
+      <c r="G74" t="s">
+        <v>1469</v>
+      </c>
       <c r="J74" t="s">
         <v>15</v>
       </c>
@@ -6558,7 +6783,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6571,6 +6796,9 @@
       <c r="F75">
         <v>6281945394717</v>
       </c>
+      <c r="G75" t="s">
+        <v>1469</v>
+      </c>
       <c r="J75" t="s">
         <v>15</v>
       </c>
@@ -6581,7 +6809,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6594,6 +6822,9 @@
       <c r="F76">
         <v>6282234560727</v>
       </c>
+      <c r="G76" t="s">
+        <v>1469</v>
+      </c>
       <c r="J76" t="s">
         <v>15</v>
       </c>
@@ -6604,7 +6835,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6617,6 +6848,9 @@
       <c r="F77">
         <v>628998815005</v>
       </c>
+      <c r="G77" t="s">
+        <v>1469</v>
+      </c>
       <c r="J77" t="s">
         <v>43</v>
       </c>
@@ -6627,7 +6861,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6640,6 +6874,9 @@
       <c r="F78">
         <v>6289661161296</v>
       </c>
+      <c r="G78" t="s">
+        <v>1469</v>
+      </c>
       <c r="J78" t="s">
         <v>15</v>
       </c>
@@ -6653,7 +6890,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6666,6 +6903,9 @@
       <c r="F79">
         <v>6285708111951</v>
       </c>
+      <c r="G79" t="s">
+        <v>1469</v>
+      </c>
       <c r="J79" t="s">
         <v>15</v>
       </c>
@@ -6676,7 +6916,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6689,6 +6929,9 @@
       <c r="F80">
         <v>6282257733991</v>
       </c>
+      <c r="G80" t="s">
+        <v>1469</v>
+      </c>
       <c r="J80" t="s">
         <v>15</v>
       </c>
@@ -6699,7 +6942,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6712,6 +6955,9 @@
       <c r="F81">
         <v>6282231648151</v>
       </c>
+      <c r="G81" t="s">
+        <v>1469</v>
+      </c>
       <c r="J81" t="s">
         <v>43</v>
       </c>
@@ -6722,7 +6968,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6735,6 +6981,9 @@
       <c r="F82">
         <v>6282115971671</v>
       </c>
+      <c r="G82" t="s">
+        <v>1469</v>
+      </c>
       <c r="J82" t="s">
         <v>15</v>
       </c>
@@ -6745,7 +6994,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -6758,6 +7007,9 @@
       <c r="F83">
         <v>6283834571565</v>
       </c>
+      <c r="G83" t="s">
+        <v>1469</v>
+      </c>
       <c r="J83" t="s">
         <v>15</v>
       </c>
@@ -6768,7 +7020,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -6781,6 +7033,9 @@
       <c r="F84">
         <v>6281359124032</v>
       </c>
+      <c r="G84" t="s">
+        <v>1469</v>
+      </c>
       <c r="J84" t="s">
         <v>15</v>
       </c>
@@ -6794,7 +7049,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -6807,6 +7062,9 @@
       <c r="F85">
         <v>6281227017063</v>
       </c>
+      <c r="G85" t="s">
+        <v>1469</v>
+      </c>
       <c r="J85" t="s">
         <v>15</v>
       </c>
@@ -6817,7 +7075,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -6830,6 +7088,9 @@
       <c r="F86">
         <v>628563525946</v>
       </c>
+      <c r="G86" t="s">
+        <v>1469</v>
+      </c>
       <c r="J86" t="s">
         <v>15</v>
       </c>
@@ -6840,7 +7101,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -6853,6 +7114,9 @@
       <c r="F87">
         <v>6285606204307</v>
       </c>
+      <c r="G87" t="s">
+        <v>1469</v>
+      </c>
       <c r="J87" t="s">
         <v>43</v>
       </c>
@@ -6863,7 +7127,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -6876,6 +7140,9 @@
       <c r="F88">
         <v>628113651076</v>
       </c>
+      <c r="G88" t="s">
+        <v>1468</v>
+      </c>
       <c r="J88" t="s">
         <v>15</v>
       </c>
@@ -6886,7 +7153,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -6899,6 +7166,9 @@
       <c r="F89">
         <v>62895367328837</v>
       </c>
+      <c r="G89" t="s">
+        <v>1468</v>
+      </c>
       <c r="J89" t="s">
         <v>15</v>
       </c>
@@ -6909,7 +7179,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -6922,6 +7192,9 @@
       <c r="F90">
         <v>6285214138886</v>
       </c>
+      <c r="G90" t="s">
+        <v>1468</v>
+      </c>
       <c r="J90" t="s">
         <v>15</v>
       </c>
@@ -6932,7 +7205,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -6945,6 +7218,9 @@
       <c r="F91">
         <v>62818381366</v>
       </c>
+      <c r="G91" t="s">
+        <v>1469</v>
+      </c>
       <c r="J91" t="s">
         <v>15</v>
       </c>
@@ -6955,7 +7231,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -6981,7 +7257,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7007,7 +7283,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7033,7 +7309,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7059,7 +7335,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7085,7 +7361,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7111,7 +7387,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7137,7 +7413,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7163,7 +7439,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7189,7 +7465,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7215,7 +7491,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7241,7 +7517,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7267,7 +7543,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7293,7 +7569,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7319,7 +7595,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7345,7 +7621,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7371,7 +7647,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7397,7 +7673,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7423,7 +7699,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7449,7 +7725,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7475,7 +7751,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7501,7 +7777,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7527,7 +7803,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7553,7 +7829,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7579,7 +7855,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7605,7 +7881,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7631,7 +7907,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7657,7 +7933,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7683,7 +7959,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7709,7 +7985,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>120</v>
       </c>
@@ -7735,7 +8011,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>121</v>
       </c>
@@ -7761,7 +8037,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>122</v>
       </c>
@@ -7787,7 +8063,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>123</v>
       </c>
@@ -7813,7 +8089,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>124</v>
       </c>
@@ -7839,7 +8115,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>125</v>
       </c>
@@ -7868,7 +8144,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>126</v>
       </c>
@@ -7894,7 +8170,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>127</v>
       </c>
@@ -7920,7 +8196,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>128</v>
       </c>
@@ -7946,7 +8222,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>129</v>
       </c>
@@ -7972,7 +8248,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>130</v>
       </c>
@@ -7998,7 +8274,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8024,7 +8300,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8050,7 +8326,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8076,7 +8352,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>134</v>
       </c>
@@ -8102,7 +8378,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>135</v>
       </c>
@@ -8128,7 +8404,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>136</v>
       </c>
@@ -8154,7 +8430,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>137</v>
       </c>
@@ -8180,7 +8456,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>138</v>
       </c>
@@ -8206,7 +8482,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8232,7 +8508,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8258,7 +8534,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8284,7 +8560,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8313,7 +8589,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8339,7 +8615,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8365,7 +8641,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8391,7 +8667,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8417,7 +8693,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8443,7 +8719,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8469,7 +8745,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8495,7 +8771,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8521,7 +8797,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8547,7 +8823,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8573,7 +8849,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8599,7 +8875,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8625,7 +8901,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8654,7 +8930,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8680,7 +8956,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8706,7 +8982,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>158</v>
       </c>
@@ -8732,7 +9008,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>159</v>
       </c>
@@ -8758,7 +9034,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>160</v>
       </c>
@@ -8784,7 +9060,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>161</v>
       </c>
@@ -8810,7 +9086,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>162</v>
       </c>
@@ -8836,7 +9112,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>163</v>
       </c>
@@ -8862,7 +9138,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>164</v>
       </c>
@@ -8888,7 +9164,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>165</v>
       </c>
@@ -8914,7 +9190,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>166</v>
       </c>
@@ -8943,7 +9219,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>167</v>
       </c>
@@ -8969,7 +9245,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>168</v>
       </c>
@@ -8995,7 +9271,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9021,7 +9297,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9047,7 +9323,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9073,7 +9349,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9099,7 +9375,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9125,7 +9401,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9151,7 +9427,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9177,7 +9453,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9203,7 +9479,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9229,7 +9505,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9255,7 +9531,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9281,7 +9557,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9307,7 +9583,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9333,7 +9609,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9359,7 +9635,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9385,7 +9661,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9411,7 +9687,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9437,7 +9713,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9463,7 +9739,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9489,7 +9765,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9515,7 +9791,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9541,7 +9817,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9567,7 +9843,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9596,7 +9872,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9622,7 +9898,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9648,7 +9924,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9674,7 +9950,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9700,7 +9976,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>196</v>
       </c>
@@ -9726,7 +10002,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>197</v>
       </c>
@@ -9752,7 +10028,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>198</v>
       </c>
@@ -9778,7 +10054,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>199</v>
       </c>
@@ -9804,7 +10080,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>200</v>
       </c>
@@ -9830,7 +10106,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>201</v>
       </c>
@@ -9856,7 +10132,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>202</v>
       </c>
@@ -9882,7 +10158,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>203</v>
       </c>
@@ -9908,7 +10184,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>204</v>
       </c>
@@ -9937,7 +10213,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>205</v>
       </c>
@@ -9963,7 +10239,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>206</v>
       </c>
@@ -9989,7 +10265,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10015,7 +10291,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10044,7 +10320,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10070,7 +10346,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10096,7 +10372,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10122,7 +10398,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10148,7 +10424,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10174,7 +10450,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10200,7 +10476,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10226,7 +10502,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10252,7 +10528,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10278,7 +10554,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10307,7 +10583,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10333,7 +10609,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10362,7 +10638,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10388,7 +10664,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>222</v>
       </c>
@@ -10414,7 +10690,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10440,7 +10716,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>224</v>
       </c>
@@ -10466,7 +10742,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>225</v>
       </c>
@@ -10492,7 +10768,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>226</v>
       </c>
@@ -10518,7 +10794,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>227</v>
       </c>
@@ -10544,7 +10820,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>228</v>
       </c>
@@ -10570,7 +10846,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>229</v>
       </c>
@@ -10596,7 +10872,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>230</v>
       </c>
@@ -10622,7 +10898,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>231</v>
       </c>
@@ -10651,7 +10927,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>232</v>
       </c>
@@ -10677,7 +10953,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>233</v>
       </c>
@@ -10703,7 +10979,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>234</v>
       </c>
@@ -10729,7 +11005,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>235</v>
       </c>
@@ -10755,7 +11031,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>236</v>
       </c>
@@ -10781,7 +11057,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>237</v>
       </c>
@@ -10807,7 +11083,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>238</v>
       </c>
@@ -10833,7 +11109,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>239</v>
       </c>
@@ -10859,7 +11135,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>240</v>
       </c>
@@ -10885,7 +11161,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>241</v>
       </c>
@@ -10911,7 +11187,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>242</v>
       </c>
@@ -10937,7 +11213,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>243</v>
       </c>
@@ -10963,7 +11239,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>244</v>
       </c>
@@ -10989,7 +11265,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11015,7 +11291,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11041,7 +11317,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11067,7 +11343,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>248</v>
       </c>
@@ -11093,7 +11369,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>249</v>
       </c>
@@ -11119,7 +11395,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>250</v>
       </c>
@@ -11145,7 +11421,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>251</v>
       </c>
@@ -11171,7 +11447,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>252</v>
       </c>
@@ -11197,7 +11473,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>253</v>
       </c>
@@ -11223,7 +11499,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>254</v>
       </c>
@@ -11249,7 +11525,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>255</v>
       </c>
@@ -11275,7 +11551,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>256</v>
       </c>
@@ -11301,7 +11577,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>257</v>
       </c>
@@ -11327,7 +11603,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>258</v>
       </c>
@@ -11353,7 +11629,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>259</v>
       </c>
@@ -11379,7 +11655,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>260</v>
       </c>
@@ -11405,7 +11681,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>261</v>
       </c>
@@ -11431,7 +11707,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>262</v>
       </c>
@@ -11457,7 +11733,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>263</v>
       </c>
@@ -11483,7 +11759,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>264</v>
       </c>
@@ -11509,7 +11785,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>265</v>
       </c>
@@ -11535,7 +11811,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>266</v>
       </c>
@@ -11561,7 +11837,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>267</v>
       </c>
@@ -11587,7 +11863,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>268</v>
       </c>
@@ -11613,7 +11889,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>269</v>
       </c>
@@ -11639,7 +11915,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>270</v>
       </c>
@@ -11665,7 +11941,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>271</v>
       </c>
@@ -11691,7 +11967,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>272</v>
       </c>
@@ -11720,7 +11996,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>273</v>
       </c>
@@ -11746,7 +12022,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>274</v>
       </c>
@@ -11772,7 +12048,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>275</v>
       </c>
@@ -11798,7 +12074,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>276</v>
       </c>
@@ -11824,7 +12100,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>277</v>
       </c>
@@ -11850,7 +12126,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>278</v>
       </c>
@@ -11879,7 +12155,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>279</v>
       </c>
@@ -11905,7 +12181,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>280</v>
       </c>
@@ -11931,7 +12207,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>281</v>
       </c>
@@ -11957,7 +12233,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>282</v>
       </c>
@@ -11983,7 +12259,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>283</v>
       </c>
@@ -12012,7 +12288,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>284</v>
       </c>
@@ -12038,7 +12314,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>285</v>
       </c>
@@ -12064,7 +12340,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>286</v>
       </c>
@@ -12090,7 +12366,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>287</v>
       </c>
@@ -12116,7 +12392,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>288</v>
       </c>
@@ -12142,7 +12418,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>289</v>
       </c>
@@ -12168,7 +12444,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>290</v>
       </c>
@@ -12194,7 +12470,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>291</v>
       </c>
@@ -12220,7 +12496,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>292</v>
       </c>
@@ -12246,7 +12522,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>293</v>
       </c>
@@ -12275,7 +12551,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>294</v>
       </c>
@@ -12301,7 +12577,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>295</v>
       </c>
@@ -12330,7 +12606,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>296</v>
       </c>
@@ -12356,7 +12632,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>297</v>
       </c>
@@ -12382,7 +12658,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>298</v>
       </c>
@@ -12408,7 +12684,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>299</v>
       </c>
@@ -12434,7 +12710,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>300</v>
       </c>
@@ -12460,7 +12736,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>301</v>
       </c>
@@ -12486,7 +12762,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>302</v>
       </c>
@@ -12512,7 +12788,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>303</v>
       </c>
@@ -12538,7 +12814,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>304</v>
       </c>
@@ -12564,7 +12840,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>305</v>
       </c>
@@ -12590,7 +12866,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>306</v>
       </c>
@@ -12616,7 +12892,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>307</v>
       </c>
@@ -12642,7 +12918,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>308</v>
       </c>
@@ -12668,7 +12944,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>309</v>
       </c>
@@ -12694,7 +12970,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>310</v>
       </c>
@@ -12720,7 +12996,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>311</v>
       </c>
@@ -12746,7 +13022,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>312</v>
       </c>
@@ -12772,7 +13048,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>313</v>
       </c>
@@ -12798,7 +13074,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>314</v>
       </c>
@@ -12824,7 +13100,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>315</v>
       </c>
@@ -12850,7 +13126,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>316</v>
       </c>
@@ -12879,7 +13155,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>317</v>
       </c>
@@ -12905,7 +13181,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>318</v>
       </c>
@@ -12931,7 +13207,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>319</v>
       </c>
@@ -12957,7 +13233,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>320</v>
       </c>
@@ -12983,7 +13259,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>321</v>
       </c>
@@ -13009,7 +13285,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>322</v>
       </c>
@@ -13035,7 +13311,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>323</v>
       </c>
@@ -13061,7 +13337,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>324</v>
       </c>
@@ -13087,7 +13363,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>325</v>
       </c>
@@ -13113,7 +13389,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>326</v>
       </c>
@@ -13139,7 +13415,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>327</v>
       </c>
@@ -13165,7 +13441,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>328</v>
       </c>
@@ -13191,7 +13467,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>329</v>
       </c>
@@ -13217,7 +13493,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>330</v>
       </c>
@@ -13246,7 +13522,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>331</v>
       </c>
@@ -13272,7 +13548,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>332</v>
       </c>
@@ -13298,7 +13574,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>333</v>
       </c>
@@ -13324,7 +13600,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>334</v>
       </c>
@@ -13350,7 +13626,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>335</v>
       </c>
@@ -13376,7 +13652,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>336</v>
       </c>
@@ -13402,7 +13678,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>337</v>
       </c>
@@ -13428,7 +13704,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>338</v>
       </c>
@@ -13454,7 +13730,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>339</v>
       </c>
@@ -13480,7 +13756,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>340</v>
       </c>
@@ -13506,7 +13782,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>341</v>
       </c>
@@ -13535,7 +13811,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>342</v>
       </c>
@@ -13561,7 +13837,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>343</v>
       </c>
@@ -13587,7 +13863,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>344</v>
       </c>
@@ -13613,7 +13889,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>345</v>
       </c>
@@ -13642,7 +13918,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>346</v>
       </c>
@@ -13668,7 +13944,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>347</v>
       </c>
@@ -13694,7 +13970,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>348</v>
       </c>
@@ -13720,7 +13996,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>349</v>
       </c>
@@ -13746,7 +14022,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>350</v>
       </c>
@@ -13772,7 +14048,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>351</v>
       </c>
@@ -13798,7 +14074,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>352</v>
       </c>
@@ -13824,7 +14100,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>353</v>
       </c>
@@ -13850,7 +14126,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>354</v>
       </c>
@@ -13876,7 +14152,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>355</v>
       </c>
@@ -13902,7 +14178,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>356</v>
       </c>
@@ -13928,7 +14204,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>357</v>
       </c>
@@ -13954,7 +14230,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>358</v>
       </c>
@@ -13980,7 +14256,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>359</v>
       </c>
@@ -14006,7 +14282,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>360</v>
       </c>
@@ -14032,7 +14308,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>361</v>
       </c>
@@ -14058,7 +14334,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>362</v>
       </c>
@@ -14084,7 +14360,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>363</v>
       </c>
@@ -14113,7 +14389,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>364</v>
       </c>
@@ -14139,7 +14415,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>365</v>
       </c>
@@ -14165,7 +14441,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>366</v>
       </c>
@@ -14191,7 +14467,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>367</v>
       </c>
@@ -14217,7 +14493,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>368</v>
       </c>
@@ -14243,7 +14519,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>369</v>
       </c>
@@ -14269,7 +14545,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>370</v>
       </c>
@@ -14298,7 +14574,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>371</v>
       </c>
@@ -14324,7 +14600,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>372</v>
       </c>
@@ -14350,7 +14626,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>373</v>
       </c>
@@ -14376,7 +14652,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>374</v>
       </c>
@@ -14405,7 +14681,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>375</v>
       </c>
@@ -14431,7 +14707,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>376</v>
       </c>
@@ -14457,7 +14733,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>377</v>
       </c>
@@ -14483,7 +14759,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>378</v>
       </c>
@@ -14509,7 +14785,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>379</v>
       </c>
@@ -14535,7 +14811,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>380</v>
       </c>
@@ -14561,7 +14837,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>381</v>
       </c>
@@ -14587,7 +14863,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>382</v>
       </c>
@@ -14613,7 +14889,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>383</v>
       </c>
@@ -14639,7 +14915,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>384</v>
       </c>
@@ -14665,7 +14941,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>385</v>
       </c>
@@ -14691,7 +14967,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>386</v>
       </c>
@@ -14717,7 +14993,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>387</v>
       </c>
@@ -14743,7 +15019,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>388</v>
       </c>
@@ -14769,7 +15045,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>389</v>
       </c>
@@ -14795,7 +15071,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>390</v>
       </c>
@@ -14821,7 +15097,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>391</v>
       </c>
@@ -14847,7 +15123,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>392</v>
       </c>
@@ -14873,7 +15149,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>393</v>
       </c>
@@ -14899,7 +15175,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>394</v>
       </c>
@@ -14925,7 +15201,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>395</v>
       </c>
@@ -14951,7 +15227,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>396</v>
       </c>
@@ -14977,7 +15253,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>397</v>
       </c>
@@ -15006,7 +15282,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>398</v>
       </c>
@@ -15032,7 +15308,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>399</v>
       </c>
@@ -15058,7 +15334,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>400</v>
       </c>
@@ -15084,7 +15360,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>401</v>
       </c>
@@ -15110,7 +15386,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>402</v>
       </c>
@@ -15136,7 +15412,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>403</v>
       </c>
@@ -15162,7 +15438,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>404</v>
       </c>
@@ -15191,7 +15467,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>405</v>
       </c>
@@ -15220,7 +15496,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>406</v>
       </c>
@@ -15246,7 +15522,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>407</v>
       </c>
@@ -15272,7 +15548,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>408</v>
       </c>
@@ -15298,7 +15574,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>409</v>
       </c>
@@ -15324,7 +15600,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>410</v>
       </c>
@@ -15350,7 +15626,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>411</v>
       </c>
@@ -15376,7 +15652,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>412</v>
       </c>
@@ -15402,7 +15678,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>413</v>
       </c>
@@ -15428,7 +15704,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>414</v>
       </c>
@@ -15454,7 +15730,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>415</v>
       </c>
@@ -15480,7 +15756,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>416</v>
       </c>
@@ -15506,7 +15782,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>417</v>
       </c>
@@ -15532,7 +15808,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>418</v>
       </c>
@@ -15558,7 +15834,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>419</v>
       </c>
@@ -15587,7 +15863,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>420</v>
       </c>
@@ -15613,7 +15889,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>421</v>
       </c>
@@ -15639,7 +15915,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>422</v>
       </c>
@@ -15665,7 +15941,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>423</v>
       </c>
@@ -15691,7 +15967,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>424</v>
       </c>
@@ -15717,7 +15993,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>425</v>
       </c>
@@ -15743,7 +16019,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>426</v>
       </c>
@@ -15769,7 +16045,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>427</v>
       </c>
@@ -15798,7 +16074,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>428</v>
       </c>
@@ -15827,7 +16103,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>429</v>
       </c>
@@ -15853,7 +16129,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>430</v>
       </c>
@@ -15879,7 +16155,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>431</v>
       </c>
@@ -15908,7 +16184,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>432</v>
       </c>
@@ -15934,7 +16210,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>433</v>
       </c>
@@ -15960,7 +16236,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>434</v>
       </c>
@@ -15989,7 +16265,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>435</v>
       </c>
@@ -16015,7 +16291,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>436</v>
       </c>
@@ -16041,7 +16317,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>437</v>
       </c>
@@ -16067,7 +16343,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>438</v>
       </c>
@@ -16096,7 +16372,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>439</v>
       </c>
@@ -16122,7 +16398,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>440</v>
       </c>
@@ -16148,7 +16424,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>441</v>
       </c>
@@ -16174,7 +16450,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>442</v>
       </c>
@@ -16200,7 +16476,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>443</v>
       </c>
@@ -16226,7 +16502,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>444</v>
       </c>
@@ -16252,7 +16528,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>445</v>
       </c>
@@ -16278,7 +16554,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>446</v>
       </c>
@@ -16307,7 +16583,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>447</v>
       </c>
@@ -16333,7 +16609,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>448</v>
       </c>
@@ -16359,7 +16635,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>449</v>
       </c>
@@ -16385,7 +16661,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>450</v>
       </c>
@@ -16411,7 +16687,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>451</v>
       </c>
@@ -16437,7 +16713,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>452</v>
       </c>
@@ -16463,7 +16739,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>453</v>
       </c>
@@ -16489,7 +16765,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>454</v>
       </c>
@@ -16515,7 +16791,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>455</v>
       </c>
@@ -16541,7 +16817,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>456</v>
       </c>
@@ -16567,7 +16843,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>457</v>
       </c>
@@ -16593,7 +16869,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>458</v>
       </c>
@@ -16619,7 +16895,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>459</v>
       </c>
@@ -16648,7 +16924,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>460</v>
       </c>
@@ -16674,7 +16950,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>461</v>
       </c>
@@ -16700,7 +16976,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>462</v>
       </c>
@@ -16729,7 +17005,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>463</v>
       </c>

--- a/reportstellarsoiree.xlsx
+++ b/reportstellarsoiree.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\TABITA\Hwa Ind Prom\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1000001_{067FECF8-0C28-954A-B5BC-8965D0D0802F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB39B9DA-0B9B-4531-A9DF-0A6102D0E832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1470">
   <si>
     <t>No</t>
   </si>
@@ -251,6 +251,9 @@
     <t>Iin Kristiani, S.Pd.</t>
   </si>
   <si>
+    <t>Tidak Hadir</t>
+  </si>
+  <si>
     <t>https://udr.reddonedigital.com/IinKristianiS.Pd./StellarSoiree/82413/375</t>
   </si>
   <si>
@@ -404,9 +407,6 @@
     <t>Christina Ratih Ayuningtyas, S.Pd.</t>
   </si>
   <si>
-    <t>Tidak Hadir</t>
-  </si>
-  <si>
     <t>Selamat atas keberhasilan kalian semua sampai pada tahap ini semoga kalian selalu menjadi insan saleh dan terpelajar dan Tetap Bersemangat</t>
   </si>
   <si>
@@ -4439,24 +4439,20 @@
     <t>12L</t>
   </si>
   <si>
+    <t>GURU DAN STAFF</t>
+  </si>
+  <si>
     <t>OSIS</t>
-  </si>
-  <si>
-    <t>GURU DAN STAFF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -4480,9 +4476,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4788,9 +4783,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M464"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4831,7 +4826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4845,7 +4840,7 @@
         <v>628170470382</v>
       </c>
       <c r="G2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J2" t="s">
         <v>15</v>
@@ -4860,7 +4855,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4874,7 +4869,7 @@
         <v>6281818137383</v>
       </c>
       <c r="G3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -4889,7 +4884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4903,7 +4898,7 @@
         <v>6281336691764</v>
       </c>
       <c r="G4" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J4" t="s">
         <v>15</v>
@@ -4915,7 +4910,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4929,7 +4924,7 @@
         <v>628179602997</v>
       </c>
       <c r="G5" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J5" t="s">
         <v>15</v>
@@ -4941,7 +4936,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4955,7 +4950,7 @@
         <v>6285649927363</v>
       </c>
       <c r="G6" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J6" t="s">
         <v>15</v>
@@ -4967,7 +4962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4981,7 +4976,7 @@
         <v>6281334792770</v>
       </c>
       <c r="G7" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J7" t="s">
         <v>15</v>
@@ -4996,7 +4991,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5010,7 +5005,7 @@
         <v>6282257634886</v>
       </c>
       <c r="G8" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J8" t="s">
         <v>15</v>
@@ -5022,7 +5017,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5036,7 +5031,7 @@
         <v>6281334151569</v>
       </c>
       <c r="G9" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J9" t="s">
         <v>15</v>
@@ -5048,7 +5043,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5062,7 +5057,7 @@
         <v>6281334450055</v>
       </c>
       <c r="G10" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J10" t="s">
         <v>43</v>
@@ -5074,7 +5069,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5088,7 +5083,7 @@
         <v>628179603425</v>
       </c>
       <c r="G11" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J11" t="s">
         <v>15</v>
@@ -5100,7 +5095,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5114,7 +5109,7 @@
         <v>6282139666128</v>
       </c>
       <c r="G12" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J12" t="s">
         <v>15</v>
@@ -5126,7 +5121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5140,7 +5135,7 @@
         <v>628175406785</v>
       </c>
       <c r="G13" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J13" t="s">
         <v>15</v>
@@ -5152,7 +5147,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5166,19 +5161,19 @@
         <v>6282148341873</v>
       </c>
       <c r="G14" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J14" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5192,7 +5187,7 @@
         <v>6281332050819</v>
       </c>
       <c r="G15" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J15" t="s">
         <v>15</v>
@@ -5207,7 +5202,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5221,7 +5216,7 @@
         <v>628123387337</v>
       </c>
       <c r="G16" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J16" t="s">
         <v>15</v>
@@ -5233,7 +5228,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5247,7 +5242,7 @@
         <v>6282139896030</v>
       </c>
       <c r="G17" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J17" t="s">
         <v>15</v>
@@ -5259,7 +5254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5273,7 +5268,7 @@
         <v>6281937799024</v>
       </c>
       <c r="G18" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J18" t="s">
         <v>15</v>
@@ -5285,7 +5280,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5299,33 +5294,33 @@
         <v>6285156164955</v>
       </c>
       <c r="G19" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J19" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="M19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20">
         <v>628155511298</v>
       </c>
       <c r="G20" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J20" t="s">
         <v>15</v>
@@ -5334,24 +5329,24 @@
         <v>1</v>
       </c>
       <c r="M20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F21">
         <v>6285790863015</v>
       </c>
       <c r="G21" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J21" t="s">
         <v>15</v>
@@ -5360,24 +5355,24 @@
         <v>1</v>
       </c>
       <c r="M21" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F22">
         <v>6282331819313</v>
       </c>
       <c r="G22" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
@@ -5386,27 +5381,27 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F23">
         <v>6281334112615</v>
       </c>
       <c r="G23" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J23" t="s">
         <v>15</v>
@@ -5415,24 +5410,24 @@
         <v>1</v>
       </c>
       <c r="M23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F24">
         <v>6281334212626</v>
       </c>
       <c r="G24" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J24" t="s">
         <v>15</v>
@@ -5441,27 +5436,27 @@
         <v>1</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F25">
         <v>6281335839249</v>
       </c>
       <c r="G25" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J25" t="s">
         <v>15</v>
@@ -5470,24 +5465,24 @@
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26">
         <v>6283848050976</v>
       </c>
       <c r="G26" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J26" t="s">
         <v>15</v>
@@ -5496,24 +5491,24 @@
         <v>1</v>
       </c>
       <c r="M26" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F27">
         <v>6281252702510</v>
       </c>
       <c r="G27" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J27" t="s">
         <v>15</v>
@@ -5522,53 +5517,53 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M27" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F28">
         <v>628563568740</v>
       </c>
       <c r="G28" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J28" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29">
         <v>6281331399677</v>
       </c>
       <c r="G29" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J29" t="s">
         <v>15</v>
@@ -5577,24 +5572,24 @@
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F30">
         <v>6281334056650</v>
       </c>
       <c r="G30" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J30" t="s">
         <v>15</v>
@@ -5603,27 +5598,27 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M30" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31">
         <v>6287701681982</v>
       </c>
       <c r="G31" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J31" t="s">
         <v>15</v>
@@ -5632,27 +5627,27 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M31" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32">
         <v>6281333400088</v>
       </c>
       <c r="G32" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J32" t="s">
         <v>15</v>
@@ -5661,27 +5656,27 @@
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F33">
         <v>6285755700531</v>
       </c>
       <c r="G33" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J33" t="s">
         <v>15</v>
@@ -5690,27 +5685,27 @@
         <v>1</v>
       </c>
       <c r="M33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F34">
         <v>628562813537</v>
       </c>
       <c r="G34" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J34" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -5722,7 +5717,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5736,7 +5731,7 @@
         <v>6281232056437</v>
       </c>
       <c r="G35" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J35" t="s">
         <v>15</v>
@@ -5748,7 +5743,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5762,7 +5757,7 @@
         <v>6285643864321</v>
       </c>
       <c r="G36" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J36" t="s">
         <v>15</v>
@@ -5774,7 +5769,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5788,7 +5783,7 @@
         <v>6281937778708</v>
       </c>
       <c r="G37" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J37" t="s">
         <v>15</v>
@@ -5800,7 +5795,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5814,7 +5809,7 @@
         <v>6285707636369</v>
       </c>
       <c r="G38" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J38" t="s">
         <v>15</v>
@@ -5826,7 +5821,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5840,7 +5835,7 @@
         <v>6281555767329</v>
       </c>
       <c r="G39" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J39" t="s">
         <v>15</v>
@@ -5852,7 +5847,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5866,7 +5861,7 @@
         <v>6282233979952</v>
       </c>
       <c r="G40" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J40" t="s">
         <v>15</v>
@@ -5878,7 +5873,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5892,7 +5887,7 @@
         <v>6282131726070</v>
       </c>
       <c r="G41" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J41" t="s">
         <v>15</v>
@@ -5904,7 +5899,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5918,10 +5913,10 @@
         <v>6287859887587</v>
       </c>
       <c r="G42" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J42" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -5933,7 +5928,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5947,7 +5942,7 @@
         <v>6285257601040</v>
       </c>
       <c r="G43" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J43" t="s">
         <v>15</v>
@@ -5962,7 +5957,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5976,7 +5971,7 @@
         <v>6281515392119</v>
       </c>
       <c r="G44" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J44" t="s">
         <v>15</v>
@@ -5988,7 +5983,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -6002,7 +5997,7 @@
         <v>6285933051018</v>
       </c>
       <c r="G45" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J45" t="s">
         <v>15</v>
@@ -6017,7 +6012,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -6031,7 +6026,7 @@
         <v>6281233516737</v>
       </c>
       <c r="G46" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J46" t="s">
         <v>15</v>
@@ -6043,7 +6038,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -6057,7 +6052,7 @@
         <v>6281216131689</v>
       </c>
       <c r="G47" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J47" t="s">
         <v>15</v>
@@ -6069,7 +6064,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -6083,7 +6078,7 @@
         <v>6285331391901</v>
       </c>
       <c r="G48" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J48" t="s">
         <v>15</v>
@@ -6095,7 +6090,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -6109,7 +6104,7 @@
         <v>6281233553418</v>
       </c>
       <c r="G49" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J49" t="s">
         <v>15</v>
@@ -6121,7 +6116,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -6135,10 +6130,10 @@
         <v>6281210849961</v>
       </c>
       <c r="G50" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J50" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -6150,7 +6145,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -6164,7 +6159,7 @@
         <v>6289660460697</v>
       </c>
       <c r="G51" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J51" t="s">
         <v>15</v>
@@ -6176,7 +6171,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -6190,7 +6185,7 @@
         <v>6281217242048</v>
       </c>
       <c r="G52" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J52" t="s">
         <v>15</v>
@@ -6202,7 +6197,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -6216,7 +6211,7 @@
         <v>6281252439951</v>
       </c>
       <c r="G53" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J53" t="s">
         <v>15</v>
@@ -6228,7 +6223,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -6242,7 +6237,7 @@
         <v>62818538879</v>
       </c>
       <c r="G54" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J54" t="s">
         <v>15</v>
@@ -6254,7 +6249,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -6268,7 +6263,7 @@
         <v>6283867272006</v>
       </c>
       <c r="G55" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J55" t="s">
         <v>15</v>
@@ -6280,7 +6275,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -6294,7 +6289,7 @@
         <v>6281230694246</v>
       </c>
       <c r="G56" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J56" t="s">
         <v>15</v>
@@ -6306,7 +6301,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -6320,7 +6315,7 @@
         <v>6285701521177</v>
       </c>
       <c r="G57" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J57" t="s">
         <v>15</v>
@@ -6332,7 +6327,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -6346,7 +6341,7 @@
         <v>628125225789</v>
       </c>
       <c r="G58" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J58" t="s">
         <v>43</v>
@@ -6358,7 +6353,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -6372,7 +6367,7 @@
         <v>6281336691763</v>
       </c>
       <c r="G59" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J59" t="s">
         <v>15</v>
@@ -6387,7 +6382,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -6401,7 +6396,7 @@
         <v>6282232323043</v>
       </c>
       <c r="G60" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J60" t="s">
         <v>15</v>
@@ -6413,7 +6408,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -6427,7 +6422,7 @@
         <v>6281934991711</v>
       </c>
       <c r="G61" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J61" t="s">
         <v>15</v>
@@ -6439,7 +6434,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -6453,7 +6448,7 @@
         <v>6287859101907</v>
       </c>
       <c r="G62" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J62" t="s">
         <v>15</v>
@@ -6465,7 +6460,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -6479,7 +6474,7 @@
         <v>6285855480996</v>
       </c>
       <c r="G63" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J63" t="s">
         <v>15</v>
@@ -6491,7 +6486,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -6505,7 +6500,7 @@
         <v>6281806020894</v>
       </c>
       <c r="G64" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J64" t="s">
         <v>15</v>
@@ -6517,7 +6512,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -6531,7 +6526,7 @@
         <v>6281230153626</v>
       </c>
       <c r="G65" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J65" t="s">
         <v>15</v>
@@ -6546,7 +6541,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -6560,10 +6555,10 @@
         <v>6283869682827</v>
       </c>
       <c r="G66" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J66" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -6572,7 +6567,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -6586,7 +6581,7 @@
         <v>6281250172072</v>
       </c>
       <c r="G67" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J67" t="s">
         <v>15</v>
@@ -6598,7 +6593,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -6612,7 +6607,7 @@
         <v>6282112194857</v>
       </c>
       <c r="G68" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J68" t="s">
         <v>15</v>
@@ -6624,7 +6619,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -6638,7 +6633,7 @@
         <v>6282136444169</v>
       </c>
       <c r="G69" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J69" t="s">
         <v>15</v>
@@ -6650,7 +6645,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -6664,7 +6659,7 @@
         <v>6281555648210</v>
       </c>
       <c r="G70" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J70" t="s">
         <v>15</v>
@@ -6679,7 +6674,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -6693,7 +6688,7 @@
         <v>6281252324420</v>
       </c>
       <c r="G71" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J71" t="s">
         <v>15</v>
@@ -6705,7 +6700,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -6719,10 +6714,10 @@
         <v>62816558122</v>
       </c>
       <c r="G72" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J72" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -6731,7 +6726,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -6745,7 +6740,7 @@
         <v>6281233294669</v>
       </c>
       <c r="G73" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J73" t="s">
         <v>15</v>
@@ -6757,7 +6752,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -6771,7 +6766,7 @@
         <v>62818384463</v>
       </c>
       <c r="G74" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
@@ -6783,7 +6778,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -6797,7 +6792,7 @@
         <v>6281945394717</v>
       </c>
       <c r="G75" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J75" t="s">
         <v>15</v>
@@ -6809,7 +6804,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -6823,7 +6818,7 @@
         <v>6282234560727</v>
       </c>
       <c r="G76" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J76" t="s">
         <v>15</v>
@@ -6835,7 +6830,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -6849,7 +6844,7 @@
         <v>628998815005</v>
       </c>
       <c r="G77" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J77" t="s">
         <v>43</v>
@@ -6861,7 +6856,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -6875,7 +6870,7 @@
         <v>6289661161296</v>
       </c>
       <c r="G78" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J78" t="s">
         <v>15</v>
@@ -6890,7 +6885,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -6904,7 +6899,7 @@
         <v>6285708111951</v>
       </c>
       <c r="G79" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J79" t="s">
         <v>15</v>
@@ -6916,7 +6911,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -6930,7 +6925,7 @@
         <v>6282257733991</v>
       </c>
       <c r="G80" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J80" t="s">
         <v>15</v>
@@ -6942,7 +6937,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -6956,7 +6951,7 @@
         <v>6282231648151</v>
       </c>
       <c r="G81" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J81" t="s">
         <v>43</v>
@@ -6968,7 +6963,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -6982,7 +6977,7 @@
         <v>6282115971671</v>
       </c>
       <c r="G82" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J82" t="s">
         <v>15</v>
@@ -6994,7 +6989,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -7008,7 +7003,7 @@
         <v>6283834571565</v>
       </c>
       <c r="G83" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J83" t="s">
         <v>15</v>
@@ -7020,7 +7015,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -7034,7 +7029,7 @@
         <v>6281359124032</v>
       </c>
       <c r="G84" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J84" t="s">
         <v>15</v>
@@ -7049,7 +7044,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -7063,7 +7058,7 @@
         <v>6281227017063</v>
       </c>
       <c r="G85" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J85" t="s">
         <v>15</v>
@@ -7075,7 +7070,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -7089,7 +7084,7 @@
         <v>628563525946</v>
       </c>
       <c r="G86" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J86" t="s">
         <v>15</v>
@@ -7101,7 +7096,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -7115,7 +7110,7 @@
         <v>6285606204307</v>
       </c>
       <c r="G87" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J87" t="s">
         <v>43</v>
@@ -7127,7 +7122,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -7141,7 +7136,7 @@
         <v>628113651076</v>
       </c>
       <c r="G88" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="J88" t="s">
         <v>15</v>
@@ -7153,7 +7148,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -7167,7 +7162,7 @@
         <v>62895367328837</v>
       </c>
       <c r="G89" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="J89" t="s">
         <v>15</v>
@@ -7179,7 +7174,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -7193,7 +7188,7 @@
         <v>6285214138886</v>
       </c>
       <c r="G90" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="J90" t="s">
         <v>15</v>
@@ -7205,7 +7200,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -7219,7 +7214,7 @@
         <v>62818381366</v>
       </c>
       <c r="G91" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="J91" t="s">
         <v>15</v>
@@ -7231,7 +7226,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -7257,7 +7252,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -7283,7 +7278,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -7309,7 +7304,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -7335,7 +7330,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -7361,7 +7356,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -7387,7 +7382,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -7413,7 +7408,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -7439,7 +7434,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -7465,7 +7460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -7491,7 +7486,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -7517,7 +7512,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -7543,7 +7538,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -7569,7 +7564,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -7595,7 +7590,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -7621,7 +7616,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -7647,7 +7642,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -7673,7 +7668,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -7699,7 +7694,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -7725,7 +7720,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -7751,7 +7746,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -7777,7 +7772,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -7803,7 +7798,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -7829,7 +7824,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -7855,7 +7850,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -7881,7 +7876,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -7907,7 +7902,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -7933,7 +7928,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -7959,7 +7954,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -7985,7 +7980,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -8011,7 +8006,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -8037,7 +8032,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -8063,7 +8058,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -8089,7 +8084,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -8115,7 +8110,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -8144,7 +8139,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -8170,7 +8165,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -8196,7 +8191,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -8213,7 +8208,7 @@
         <v>1457</v>
       </c>
       <c r="J129" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K129">
         <v>0</v>
@@ -8222,7 +8217,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -8248,7 +8243,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -8274,7 +8269,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -8300,7 +8295,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -8326,7 +8321,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -8352,7 +8347,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -8378,7 +8373,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -8404,7 +8399,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -8430,7 +8425,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -8456,7 +8451,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -8482,7 +8477,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -8508,7 +8503,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -8534,7 +8529,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -8560,7 +8555,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -8589,7 +8584,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -8615,7 +8610,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -8641,7 +8636,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -8667,7 +8662,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -8693,7 +8688,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -8719,7 +8714,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -8745,7 +8740,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -8771,7 +8766,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -8797,7 +8792,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -8823,7 +8818,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -8849,7 +8844,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -8875,7 +8870,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -8901,7 +8896,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -8930,7 +8925,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -8956,7 +8951,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -8973,16 +8968,16 @@
         <v>1458</v>
       </c>
       <c r="J158" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -9008,7 +9003,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -9034,7 +9029,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -9060,7 +9055,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -9086,7 +9081,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -9112,7 +9107,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -9138,7 +9133,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -9164,7 +9159,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -9190,7 +9185,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -9219,7 +9214,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -9245,7 +9240,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -9271,7 +9266,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -9297,7 +9292,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="171" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -9323,7 +9318,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -9349,7 +9344,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -9375,7 +9370,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -9401,7 +9396,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -9427,7 +9422,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -9453,7 +9448,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -9479,7 +9474,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -9505,7 +9500,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -9531,7 +9526,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -9557,7 +9552,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -9583,7 +9578,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -9609,7 +9604,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -9635,7 +9630,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -9661,7 +9656,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -9687,7 +9682,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -9713,7 +9708,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -9739,7 +9734,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -9765,7 +9760,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -9791,7 +9786,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -9817,7 +9812,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -9843,7 +9838,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -9872,7 +9867,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -9898,7 +9893,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -9924,7 +9919,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -9950,7 +9945,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -9976,7 +9971,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -10002,7 +9997,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -10028,7 +10023,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -10054,7 +10049,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -10080,7 +10075,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -10106,7 +10101,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -10132,7 +10127,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -10158,7 +10153,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -10184,7 +10179,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -10213,7 +10208,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -10239,7 +10234,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -10265,7 +10260,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -10291,7 +10286,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -10320,7 +10315,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -10346,7 +10341,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -10372,7 +10367,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -10398,7 +10393,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -10424,7 +10419,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -10450,7 +10445,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -10476,7 +10471,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -10502,7 +10497,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -10528,7 +10523,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -10554,7 +10549,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -10583,7 +10578,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -10596,7 +10591,7 @@
       <c r="F220">
         <v>6282142492145</v>
       </c>
-      <c r="G220" s="1" t="s">
+      <c r="G220" t="s">
         <v>1460</v>
       </c>
       <c r="J220" t="s">
@@ -10609,7 +10604,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -10622,7 +10617,7 @@
       <c r="F221">
         <v>6281236119406</v>
       </c>
-      <c r="G221" s="1" t="s">
+      <c r="G221" t="s">
         <v>1460</v>
       </c>
       <c r="J221" t="s">
@@ -10638,7 +10633,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -10651,7 +10646,7 @@
       <c r="F222">
         <v>6281559801387</v>
       </c>
-      <c r="G222" s="1" t="s">
+      <c r="G222" t="s">
         <v>1460</v>
       </c>
       <c r="J222" t="s">
@@ -10664,7 +10659,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -10677,7 +10672,7 @@
       <c r="F223">
         <v>6287859595928</v>
       </c>
-      <c r="G223" s="1" t="s">
+      <c r="G223" t="s">
         <v>1460</v>
       </c>
       <c r="J223" t="s">
@@ -10690,7 +10685,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -10703,7 +10698,7 @@
       <c r="F224">
         <v>6287779273966</v>
       </c>
-      <c r="G224" s="1" t="s">
+      <c r="G224" t="s">
         <v>1460</v>
       </c>
       <c r="J224" t="s">
@@ -10716,7 +10711,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -10729,7 +10724,7 @@
       <c r="F225">
         <v>628113042112</v>
       </c>
-      <c r="G225" s="1" t="s">
+      <c r="G225" t="s">
         <v>1460</v>
       </c>
       <c r="J225" t="s">
@@ -10742,7 +10737,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -10755,7 +10750,7 @@
       <c r="F226">
         <v>6282191225567</v>
       </c>
-      <c r="G226" s="1" t="s">
+      <c r="G226" t="s">
         <v>1460</v>
       </c>
       <c r="J226" t="s">
@@ -10768,7 +10763,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -10781,7 +10776,7 @@
       <c r="F227">
         <v>62881026473277</v>
       </c>
-      <c r="G227" s="1" t="s">
+      <c r="G227" t="s">
         <v>1460</v>
       </c>
       <c r="J227" t="s">
@@ -10794,7 +10789,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -10807,7 +10802,7 @@
       <c r="F228">
         <v>6281359230611</v>
       </c>
-      <c r="G228" s="1" t="s">
+      <c r="G228" t="s">
         <v>1460</v>
       </c>
       <c r="J228" t="s">
@@ -10820,7 +10815,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -10833,7 +10828,7 @@
       <c r="F229">
         <v>6281216058301</v>
       </c>
-      <c r="G229" s="1" t="s">
+      <c r="G229" t="s">
         <v>1460</v>
       </c>
       <c r="J229" t="s">
@@ -10846,7 +10841,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -10859,7 +10854,7 @@
       <c r="F230">
         <v>6281251094584</v>
       </c>
-      <c r="G230" s="1" t="s">
+      <c r="G230" t="s">
         <v>1460</v>
       </c>
       <c r="J230" t="s">
@@ -10872,7 +10867,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -10885,7 +10880,7 @@
       <c r="F231">
         <v>6289686105579</v>
       </c>
-      <c r="G231" s="1" t="s">
+      <c r="G231" t="s">
         <v>1460</v>
       </c>
       <c r="J231" t="s">
@@ -10898,7 +10893,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -10911,7 +10906,7 @@
       <c r="F232">
         <v>6285384984543</v>
       </c>
-      <c r="G232" s="1" t="s">
+      <c r="G232" t="s">
         <v>1460</v>
       </c>
       <c r="J232" t="s">
@@ -10927,7 +10922,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -10940,7 +10935,7 @@
       <c r="F233">
         <v>6285257140633</v>
       </c>
-      <c r="G233" s="1" t="s">
+      <c r="G233" t="s">
         <v>1460</v>
       </c>
       <c r="J233" t="s">
@@ -10953,7 +10948,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -10966,7 +10961,7 @@
       <c r="F234">
         <v>628113578875</v>
       </c>
-      <c r="G234" s="1" t="s">
+      <c r="G234" t="s">
         <v>1460</v>
       </c>
       <c r="J234" t="s">
@@ -10979,7 +10974,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -10992,7 +10987,7 @@
       <c r="F235">
         <v>6282123459682</v>
       </c>
-      <c r="G235" s="1" t="s">
+      <c r="G235" t="s">
         <v>1460</v>
       </c>
       <c r="J235" t="s">
@@ -11005,7 +11000,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -11018,7 +11013,7 @@
       <c r="F236">
         <v>6289515692970</v>
       </c>
-      <c r="G236" s="1" t="s">
+      <c r="G236" t="s">
         <v>1460</v>
       </c>
       <c r="J236" t="s">
@@ -11031,7 +11026,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -11044,7 +11039,7 @@
       <c r="F237">
         <v>628123561562</v>
       </c>
-      <c r="G237" s="1" t="s">
+      <c r="G237" t="s">
         <v>1460</v>
       </c>
       <c r="J237" t="s">
@@ -11057,7 +11052,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -11070,7 +11065,7 @@
       <c r="F238">
         <v>628114500332</v>
       </c>
-      <c r="G238" s="1" t="s">
+      <c r="G238" t="s">
         <v>1460</v>
       </c>
       <c r="J238" t="s">
@@ -11083,7 +11078,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -11096,7 +11091,7 @@
       <c r="F239">
         <v>6285732999448</v>
       </c>
-      <c r="G239" s="1" t="s">
+      <c r="G239" t="s">
         <v>1460</v>
       </c>
       <c r="J239" t="s">
@@ -11109,7 +11104,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -11122,7 +11117,7 @@
       <c r="F240">
         <v>6282142892699</v>
       </c>
-      <c r="G240" s="1" t="s">
+      <c r="G240" t="s">
         <v>1460</v>
       </c>
       <c r="J240" t="s">
@@ -11135,7 +11130,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -11148,7 +11143,7 @@
       <c r="F241">
         <v>6289506615606</v>
       </c>
-      <c r="G241" s="1" t="s">
+      <c r="G241" t="s">
         <v>1460</v>
       </c>
       <c r="J241" t="s">
@@ -11161,7 +11156,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -11174,7 +11169,7 @@
       <c r="F242">
         <v>6289691964105</v>
       </c>
-      <c r="G242" s="1" t="s">
+      <c r="G242" t="s">
         <v>1460</v>
       </c>
       <c r="J242" t="s">
@@ -11187,7 +11182,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -11200,7 +11195,7 @@
       <c r="F243">
         <v>6281335126094</v>
       </c>
-      <c r="G243" s="1" t="s">
+      <c r="G243" t="s">
         <v>1460</v>
       </c>
       <c r="J243" t="s">
@@ -11213,7 +11208,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -11226,7 +11221,7 @@
       <c r="F244">
         <v>628113008411</v>
       </c>
-      <c r="G244" s="1" t="s">
+      <c r="G244" t="s">
         <v>1460</v>
       </c>
       <c r="J244" t="s">
@@ -11239,7 +11234,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -11252,7 +11247,7 @@
       <c r="F245">
         <v>6282247622109</v>
       </c>
-      <c r="G245" s="1" t="s">
+      <c r="G245" t="s">
         <v>1460</v>
       </c>
       <c r="J245" t="s">
@@ -11265,7 +11260,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -11278,7 +11273,7 @@
       <c r="F246">
         <v>6285858888011</v>
       </c>
-      <c r="G246" s="1" t="s">
+      <c r="G246" t="s">
         <v>1460</v>
       </c>
       <c r="J246" t="s">
@@ -11291,7 +11286,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -11304,7 +11299,7 @@
       <c r="F247">
         <v>6281931435856</v>
       </c>
-      <c r="G247" s="1" t="s">
+      <c r="G247" t="s">
         <v>1460</v>
       </c>
       <c r="J247" t="s">
@@ -11317,7 +11312,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -11330,7 +11325,7 @@
       <c r="F248">
         <v>628114803123</v>
       </c>
-      <c r="G248" s="1" t="s">
+      <c r="G248" t="s">
         <v>1460</v>
       </c>
       <c r="J248" t="s">
@@ -11343,7 +11338,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -11356,7 +11351,7 @@
       <c r="F249">
         <v>6281358954498</v>
       </c>
-      <c r="G249" s="1" t="s">
+      <c r="G249" t="s">
         <v>1460</v>
       </c>
       <c r="J249" t="s">
@@ -11369,7 +11364,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -11382,7 +11377,7 @@
       <c r="F250">
         <v>6281247880690</v>
       </c>
-      <c r="G250" s="1" t="s">
+      <c r="G250" t="s">
         <v>1460</v>
       </c>
       <c r="J250" t="s">
@@ -11395,7 +11390,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -11408,7 +11403,7 @@
       <c r="F251">
         <v>6282334314822</v>
       </c>
-      <c r="G251" s="1" t="s">
+      <c r="G251" t="s">
         <v>1460</v>
       </c>
       <c r="J251" t="s">
@@ -11421,7 +11416,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -11447,7 +11442,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -11473,7 +11468,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -11499,7 +11494,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -11525,7 +11520,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -11551,7 +11546,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -11577,7 +11572,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -11603,7 +11598,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -11629,7 +11624,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="260" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -11655,7 +11650,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -11681,7 +11676,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -11707,7 +11702,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -11733,7 +11728,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -11759,7 +11754,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -11785,7 +11780,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -11811,7 +11806,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -11837,7 +11832,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -11863,7 +11858,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -11889,7 +11884,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -11915,7 +11910,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -11941,7 +11936,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -11967,7 +11962,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -11996,7 +11991,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -12022,7 +12017,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -12048,7 +12043,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -12074,7 +12069,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -12100,7 +12095,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -12126,7 +12121,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -12155,7 +12150,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -12181,7 +12176,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -12207,7 +12202,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -12233,7 +12228,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="283" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -12259,7 +12254,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -12288,7 +12283,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -12314,7 +12309,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -12340,7 +12335,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -12366,7 +12361,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -12392,7 +12387,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -12418,7 +12413,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -12444,7 +12439,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="291" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -12470,7 +12465,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -12496,7 +12491,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -12522,7 +12517,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -12551,7 +12546,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -12577,7 +12572,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -12606,7 +12601,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -12632,7 +12627,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -12658,7 +12653,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -12684,7 +12679,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -12710,7 +12705,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -12736,7 +12731,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -12762,7 +12757,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -12788,7 +12783,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -12814,7 +12809,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -12840,7 +12835,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -12866,7 +12861,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -12892,7 +12887,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -12918,7 +12913,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -12944,7 +12939,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -12970,7 +12965,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -12996,7 +12991,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -13022,7 +13017,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -13048,7 +13043,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -13074,7 +13069,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -13100,7 +13095,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -13126,7 +13121,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -13155,7 +13150,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -13181,7 +13176,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -13207,7 +13202,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -13233,7 +13228,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -13259,7 +13254,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -13285,7 +13280,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -13311,7 +13306,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -13337,7 +13332,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -13363,7 +13358,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -13389,7 +13384,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -13415,7 +13410,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -13441,7 +13436,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -13467,7 +13462,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -13493,7 +13488,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -13522,7 +13517,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -13548,7 +13543,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -13574,7 +13569,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -13600,7 +13595,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -13626,7 +13621,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -13652,7 +13647,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -13678,7 +13673,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -13704,7 +13699,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -13730,7 +13725,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -13756,7 +13751,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -13782,7 +13777,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>341</v>
       </c>
@@ -13811,7 +13806,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -13837,7 +13832,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>343</v>
       </c>
@@ -13863,7 +13858,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>344</v>
       </c>
@@ -13889,7 +13884,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>345</v>
       </c>
@@ -13918,7 +13913,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -13944,7 +13939,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>347</v>
       </c>
@@ -13970,7 +13965,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -13996,7 +13991,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -14022,7 +14017,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -14039,7 +14034,7 @@
         <v>1464</v>
       </c>
       <c r="J351" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K351">
         <v>0</v>
@@ -14048,7 +14043,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>351</v>
       </c>
@@ -14074,7 +14069,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -14100,7 +14095,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>353</v>
       </c>
@@ -14126,7 +14121,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -14152,7 +14147,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>355</v>
       </c>
@@ -14178,7 +14173,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>356</v>
       </c>
@@ -14204,7 +14199,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>357</v>
       </c>
@@ -14230,7 +14225,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -14256,7 +14251,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="360" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -14282,7 +14277,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="361" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>360</v>
       </c>
@@ -14308,7 +14303,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="362" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -14334,7 +14329,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>362</v>
       </c>
@@ -14360,7 +14355,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -14389,7 +14384,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -14415,7 +14410,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -14441,7 +14436,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>366</v>
       </c>
@@ -14467,7 +14462,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -14493,7 +14488,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -14519,7 +14514,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -14545,7 +14540,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -14574,7 +14569,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -14600,7 +14595,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>372</v>
       </c>
@@ -14626,7 +14621,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>373</v>
       </c>
@@ -14652,7 +14647,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>374</v>
       </c>
@@ -14681,7 +14676,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>375</v>
       </c>
@@ -14707,7 +14702,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>376</v>
       </c>
@@ -14733,7 +14728,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>377</v>
       </c>
@@ -14759,7 +14754,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>378</v>
       </c>
@@ -14785,7 +14780,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>379</v>
       </c>
@@ -14811,7 +14806,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -14837,7 +14832,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -14863,7 +14858,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -14889,7 +14884,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -14915,7 +14910,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -14941,7 +14936,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>385</v>
       </c>
@@ -14967,7 +14962,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>386</v>
       </c>
@@ -14993,7 +14988,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>387</v>
       </c>
@@ -15019,7 +15014,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -15045,7 +15040,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -15071,7 +15066,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -15097,7 +15092,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -15123,7 +15118,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -15149,7 +15144,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>393</v>
       </c>
@@ -15166,7 +15161,7 @@
         <v>1465</v>
       </c>
       <c r="J394" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K394">
         <v>0</v>
@@ -15175,7 +15170,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="395" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -15201,7 +15196,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>395</v>
       </c>
@@ -15227,7 +15222,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -15253,7 +15248,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -15282,7 +15277,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -15308,7 +15303,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -15334,7 +15329,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -15360,7 +15355,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -15386,7 +15381,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>402</v>
       </c>
@@ -15412,7 +15407,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>403</v>
       </c>
@@ -15438,7 +15433,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -15467,7 +15462,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="406" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -15496,7 +15491,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -15522,7 +15517,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>407</v>
       </c>
@@ -15548,7 +15543,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -15574,7 +15569,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>409</v>
       </c>
@@ -15600,7 +15595,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>410</v>
       </c>
@@ -15626,7 +15621,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -15652,7 +15647,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>412</v>
       </c>
@@ -15678,7 +15673,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -15704,7 +15699,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -15730,7 +15725,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>415</v>
       </c>
@@ -15756,7 +15751,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -15782,7 +15777,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>417</v>
       </c>
@@ -15808,7 +15803,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>418</v>
       </c>
@@ -15834,7 +15829,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>419</v>
       </c>
@@ -15863,7 +15858,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>420</v>
       </c>
@@ -15889,7 +15884,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="422" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>421</v>
       </c>
@@ -15906,7 +15901,7 @@
         <v>1466</v>
       </c>
       <c r="J422" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K422">
         <v>0</v>
@@ -15915,7 +15910,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>422</v>
       </c>
@@ -15941,7 +15936,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>423</v>
       </c>
@@ -15967,7 +15962,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>424</v>
       </c>
@@ -15993,7 +15988,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>425</v>
       </c>
@@ -16019,7 +16014,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>426</v>
       </c>
@@ -16045,7 +16040,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>427</v>
       </c>
@@ -16074,7 +16069,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="429" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>428</v>
       </c>
@@ -16103,7 +16098,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -16129,7 +16124,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>430</v>
       </c>
@@ -16155,7 +16150,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>431</v>
       </c>
@@ -16184,7 +16179,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>432</v>
       </c>
@@ -16210,7 +16205,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>433</v>
       </c>
@@ -16236,7 +16231,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>434</v>
       </c>
@@ -16265,7 +16260,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>435</v>
       </c>
@@ -16291,7 +16286,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>436</v>
       </c>
@@ -16317,7 +16312,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>437</v>
       </c>
@@ -16343,7 +16338,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="439" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>438</v>
       </c>
@@ -16372,7 +16367,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>439</v>
       </c>
@@ -16398,7 +16393,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>440</v>
       </c>
@@ -16424,7 +16419,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>441</v>
       </c>
@@ -16450,7 +16445,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>442</v>
       </c>
@@ -16476,7 +16471,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>443</v>
       </c>
@@ -16502,7 +16497,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>444</v>
       </c>
@@ -16528,7 +16523,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>445</v>
       </c>
@@ -16554,7 +16549,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>446</v>
       </c>
@@ -16583,7 +16578,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>447</v>
       </c>
@@ -16609,7 +16604,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>448</v>
       </c>
@@ -16635,7 +16630,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>449</v>
       </c>
@@ -16661,7 +16656,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>450</v>
       </c>
@@ -16687,7 +16682,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>451</v>
       </c>
@@ -16713,7 +16708,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>452</v>
       </c>
@@ -16739,7 +16734,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>453</v>
       </c>
@@ -16765,7 +16760,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>454</v>
       </c>
@@ -16782,7 +16777,7 @@
         <v>1467</v>
       </c>
       <c r="J455" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="K455">
         <v>0</v>
@@ -16791,7 +16786,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>455</v>
       </c>
@@ -16817,7 +16812,7 @@
         <v>1430</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>456</v>
       </c>
@@ -16843,7 +16838,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>457</v>
       </c>
@@ -16869,7 +16864,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>458</v>
       </c>
@@ -16895,7 +16890,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>459</v>
       </c>
@@ -16924,7 +16919,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>460</v>
       </c>
@@ -16950,7 +16945,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>461</v>
       </c>
@@ -16976,7 +16971,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>462</v>
       </c>
@@ -17005,7 +17000,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>463</v>
       </c>
@@ -17032,7 +17027,6 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>